--- a/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
+++ b/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYDATA\Project\webte\te-upgris\src\data\dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE6657A-3E28-475F-A8F5-6A65E67CABC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC92D08F-DF86-436B-B2F6-880A07AE6576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="beranda" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,12 @@
     <sheet name="slideshow" sheetId="12" r:id="rId12"/>
     <sheet name="spmi" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="672">
   <si>
     <t>videoUrl</t>
   </si>
@@ -400,12 +400,6 @@
     <t>Sistem Tenaga Listrik &amp; Smart Grid</t>
   </si>
   <si>
-    <t>S3 — Universitas Gadjah Mada</t>
-  </si>
-  <si>
-    <t>Sistem Tenaga Listrik, Analisis Sistem Daya, Pembangkit Energi Terbarukan</t>
-  </si>
-  <si>
     <t>PII, Sertifikasi Dosen</t>
   </si>
   <si>
@@ -427,15 +421,6 @@
     <t>Elektronika &amp; Sistem Kontrol</t>
   </si>
   <si>
-    <t>S2 — Institut Teknologi Bandung</t>
-  </si>
-  <si>
-    <t>Elektronika Daya, Sistem Kontrol Otomatis, PLC &amp; SCADA</t>
-  </si>
-  <si>
-    <t>BNSP Teknik Elektronika</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123457</t>
   </si>
   <si>
@@ -445,15 +430,6 @@
     <t>Telekomunikasi &amp; Jaringan</t>
   </si>
   <si>
-    <t>S2 — Universitas Diponegoro</t>
-  </si>
-  <si>
-    <t>Sistem Telekomunikasi, Jaringan Komputer, Antena &amp; Propagasi</t>
-  </si>
-  <si>
-    <t>Cisco CCNA</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123458</t>
   </si>
   <si>
@@ -463,15 +439,6 @@
     <t>Instrumentasi &amp; Pengukuran</t>
   </si>
   <si>
-    <t>S2 — Universitas Gadjah Mada</t>
-  </si>
-  <si>
-    <t>Instrumentasi Industri, Sensor &amp; Aktuator, Pengukuran Listrik</t>
-  </si>
-  <si>
-    <t>PII</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123459</t>
   </si>
   <si>
@@ -484,12 +451,6 @@
     <t>Internet of Things &amp; Embedded Systems</t>
   </si>
   <si>
-    <t>S2 — Universitas Indonesia</t>
-  </si>
-  <si>
-    <t>Mikrokontroler &amp; Embedded System, IoT, Pemrograman Sistem Tertanam</t>
-  </si>
-  <si>
     <t>BNSP IoT</t>
   </si>
   <si>
@@ -502,15 +463,6 @@
     <t>Energi Terbarukan &amp; Efisiensi Energi</t>
   </si>
   <si>
-    <t>S2 — Institut Teknologi Sepuluh Nopember</t>
-  </si>
-  <si>
-    <t>Energi Terbarukan, Konservasi Energi, Panel Surya &amp; PLTS</t>
-  </si>
-  <si>
-    <t>Auditor Energi BNSP</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123461</t>
   </si>
   <si>
@@ -520,12 +472,6 @@
     <t>Robotika &amp; Otomasi</t>
   </si>
   <si>
-    <t>Robotika, Otomasi Industri, Mekatronika</t>
-  </si>
-  <si>
-    <t>BNSP Robotik</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123462</t>
   </si>
   <si>
@@ -535,12 +481,6 @@
     <t>Kecerdasan Buatan &amp; Pemrosesan Sinyal</t>
   </si>
   <si>
-    <t>Pemrosesan Sinyal Digital, Kecerdasan Buatan, Machine Learning untuk Teknik</t>
-  </si>
-  <si>
-    <t>Google TensorFlow Developer</t>
-  </si>
-  <si>
     <t>https://sinta.kemdikbud.go.id/authors/profile/123463</t>
   </si>
   <si>
@@ -997,67 +937,16 @@
     <t>roadmap</t>
   </si>
   <si>
-    <t>Optimasi Smart Grid Berbasis Algoritma Particle Swarm Optimization untuk Distribusi Energi Terbarukan</t>
-  </si>
-  <si>
-    <t>Dr Adhi Kusmanto, S.T., M.Eng.</t>
-  </si>
-  <si>
     <t>TS</t>
   </si>
   <si>
-    <t>Rp 85.000.000</t>
-  </si>
-  <si>
     <t>Dikti</t>
   </si>
   <si>
-    <t>Sistem Energi Cerdas</t>
-  </si>
-  <si>
-    <t>https://images.unsplash.com/photo-1473341304170-971dccb5ac1e?w=600&amp;q=70</t>
-  </si>
-  <si>
-    <t>/content/penelitian/penelitian-1.md</t>
-  </si>
-  <si>
-    <t>Sistem Monitoring Kualitas Daya Listrik Berbasis IoT untuk Industri Manufaktur</t>
-  </si>
-  <si>
-    <t>Rp 60.000.000</t>
-  </si>
-  <si>
     <t>Internal Lembaga</t>
   </si>
   <si>
-    <t>Otomasi Industri</t>
-  </si>
-  <si>
-    <t>https://images.unsplash.com/photo-1581092921461-7031e4bfb83e?w=600&amp;q=70</t>
-  </si>
-  <si>
-    <t>Pengembangan Robot Inspeksi Saluran Tegangan Tinggi dengan Computer Vision</t>
-  </si>
-  <si>
     <t>TS-1</t>
-  </si>
-  <si>
-    <t>Rp 75.000.000</t>
-  </si>
-  <si>
-    <t>https://images.unsplash.com/photo-1485827404703-89b55fcc595e?w=600&amp;q=70</t>
-  </si>
-  <si>
-    <t>/content/penelitian/penelitian-3.md</t>
-  </si>
-  <si>
-    <t>Klasifikasi Gangguan Sistem Tenaga Listrik Menggunakan Deep Learning</t>
-  </si>
-  <si>
-    <t>Rp 50.000.000</t>
-  </si>
-  <si>
-    <t>AI untuk Sistem Tenaga</t>
   </si>
   <si>
     <t>deskripsi</t>
@@ -1653,6 +1542,532 @@
   </si>
   <si>
     <t>0608108204</t>
+  </si>
+  <si>
+    <t>Teknik Elektro, UGM / Tenaga Listrik</t>
+  </si>
+  <si>
+    <t>Teknik Elektro UGM / Sistem Kendali</t>
+  </si>
+  <si>
+    <t>Teknik Elektro, UGM / Jaringan Komputer</t>
+  </si>
+  <si>
+    <t>Teknik Elektro, UNDIP / Telekomunikasi</t>
+  </si>
+  <si>
+    <t>Fisika, UGM / Konversi Energi</t>
+  </si>
+  <si>
+    <t>Fisika, UGM / Material Teknik</t>
+  </si>
+  <si>
+    <t>Konversi Energi</t>
+  </si>
+  <si>
+    <t>Pembangkit Listrik Energi Terbarukan, Teknik Kontrol Digital, Metodologi Penelitian</t>
+  </si>
+  <si>
+    <t>Rangkaian Listrik,
+analisis Tenaga Listrik</t>
+  </si>
+  <si>
+    <t>Jaringan Komputer, Elektronika Digital, Matematika Diskret</t>
+  </si>
+  <si>
+    <t>Dasar Telekomunikasi, Pengolahan Citra, Teknologi Informasi, Antarmuka dan Arsitektur Komputer, Jaringan komputer</t>
+  </si>
+  <si>
+    <t>Pengolahan Citra, sensor tranduser</t>
+  </si>
+  <si>
+    <t>Bahan-bahan Listrik, Sensor dan Tranduser, Fisika Listrik</t>
+  </si>
+  <si>
+    <t>BNSP Tenaga Listrik</t>
+  </si>
+  <si>
+    <t>BNSP Otomasi Industri</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN STADIOMETER DIGITAL UNTUK DETEKSI DINI RISIKO STUNTING PADA ANAK-ANAK USIA DI BAWAH 5 TAHUN</t>
+  </si>
+  <si>
+    <t>DESAIN SISTEM KENDALI SUHU RUANG PEMANAS DENGAN METODE ULTIMATE CYCLE</t>
+  </si>
+  <si>
+    <t>EKSTRAKSI KARAGENAN RUMPUT LAUT (GRACILARIA GIGAS) MENGGUNAKAN METODE REFLUKS DAN PENGAPLIKASIANNYA PADA ENKAPSULAN EKSTRAK KULIT BUAH MANGGIS (GARCINIA MANGOSTANA L.)</t>
+  </si>
+  <si>
+    <t>PEMANFAATAN AERATOR BERPENGGERAK TURBIN SAVONIUS DARRIEUS UNTUK PENINGKATAN HASIL PRODUKSI PADA TAMBAK PEMBESARAN IKAN BANDENG (CHANOS CHANOS FORSKAL)</t>
+  </si>
+  <si>
+    <t>PENINGKATAN DAYA PV TERHUBUNG KE GRID DENGAN KOORDINASI KONTROL MPPT</t>
+  </si>
+  <si>
+    <t>DESAIN MODEL FUZZY LOGIC UNTUK PENILAIAN KUALITAS AIR SUMUR BERDASARKAN PARAMETER SALINITAS, PH, DAN KEKERUHAN DI SEMARANG</t>
+  </si>
+  <si>
+    <t>PENGELOLAAN BANJIR DENGAN SISTEM POLDER BERBASIS TEKNOLOGI INFORMASI DAN IOT</t>
+  </si>
+  <si>
+    <t>DESAIN MULTI-KONVERTER UNTUK PENGATURAN TEGANGAN DC MIKROGRID DENGAN FUZZY LOGIC</t>
+  </si>
+  <si>
+    <t>DESAIN BATERAI INVERTER SATU FASA DENGAN KONTROL PI-FUZZY UNTUK PENINGKATAN STABILITAS DAYA AC MIKROGRID</t>
+  </si>
+  <si>
+    <t>PRODUK INOVASI TEKNOLOGI HYBRID POMPA AIR MENGGUNAKAN INTERNET OF THING (IOT), WIND TURBINE DAN SOLAR PANEL SEBAGAI SALAH SATU SOLUSI PENGAIRAN AIR SAWAH DI WILAYAH DEMAK</t>
+  </si>
+  <si>
+    <t>OPTIMASI PENDINGIN TERMOAKUSTIK DENGAN TENAGA MESIN TERMOAKUSTIK MEMANFAATKAN LIMBAH PANAS DAN MATAHARI</t>
+  </si>
+  <si>
+    <t>Formulasi Pembelajaran Fisika Kontekstual Berorientasi Swasembada Energi Untuk Meningkatkan Literasi Energi Siswa</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN MEDIA PEMBELAJARAN FISIKA BERBASIS KERANGKA KERJA DEEP LEARNING UNTUK MENINGKATKAN MINAT BELAJAR DAN KEMAMPUAN PEMECAHAN MASALAH SISWA</t>
+  </si>
+  <si>
+    <t>RANCANG BANGUN PROTOTYPE ALAT UKUR POSISI BENDA BERBASIS CITRA STEREOSKOPIK</t>
+  </si>
+  <si>
+    <t>STUDY ON LOW SYMMETRY EFFECT OF A2BF6 CRYSTALS DOPED MN4+</t>
+  </si>
+  <si>
+    <t>TRACER STUDY PENDIDIKAN FISIKA UNIVERSITAS PGRI SEMARANG PADA ALUMNI LULUSAN TAHUN 2018-2022</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN E-LKPD BERBASIS MASALAH POKOK BAHASAN PENGUKURAN BESARAN FISIS UNTUK MENINGKATKAN PEMAHANAN KONSEP DAN KEMAMPUAN PENGAMBILAN KEPUTUSAN</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN E-LKPD BERBASIS PENYELESAIAN MASALAH PADA POKOK BAHASAN ENERGI TERBARUKAN UNTUK MENINGKATKAN PEMAHAMAN KONSEP DAN PENGAMBILAN KEPUTUSAN</t>
+  </si>
+  <si>
+    <t>PROFIL MINAT SISWA SLTA DALAM MELANJUTKAN STUDI DI PERGURAN TINGGI</t>
+  </si>
+  <si>
+    <t>PENERAPAN PROJEK BASED LEARNING (PJBL) UNTUK MENINGKATKAN KREATIVITAS DAN KETERAMPILAN KERJASAMA PESERTA DIDIK DALAM PEMBELAJARAN FISIKA</t>
+  </si>
+  <si>
+    <t>PREPARASI DAN OPTIMASI KETEBALAN LAPISAN TUNGGAL BAHAN NON MAGNETIK ENCENG GONDOK MENGGUNAKAN MATLAB SEBAGAI RADAR ABSORBER MATERIAL</t>
+  </si>
+  <si>
+    <t>Studi Sifat Optik Fosfor Merah berbasis Hafnium (Hf) untuk White LED</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN ALAT PERAGA ENERGI TERBARUKAN BERBASIS IOT DENGAN PENDEKATAN ESD UNTUK MENINGKATKAN KETERAMPILAN GENERIK SAINS</t>
+  </si>
+  <si>
+    <t>Studi Pengaruh Jenis, Komposisi, dan Tekanan Gas Kerja Terhadap Kinerja Pembangkit Listrik Termoakustik</t>
+  </si>
+  <si>
+    <t>KONVERSI ENERGI PANAS MENJADI ENERGI AKUSTIK
+DARI MESIN TERMOAKUSTIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengembangan Peredam Panas Ramah Lingkungan pada Atap Bangunan Berbasis Serat Kelapa
+</t>
+  </si>
+  <si>
+    <t>Ekstraksi Karagenan Rumput Laut (Gracilaria gigas) Menggunakan Metode Refluks dan Pengaplikasiannya pada Enkapsulan Ekstrak Kulit Buah Manggis (Garcinia mangostana L.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEMANFAATAN AERATOR BERPENGGERAK TURBIN SAVONIUS DARRIEUS UNTUK PENINGKATAN HASIL PRODUKSI PADA TAMBAK PEMBESARAN IKAN BANDENG (Chanos Chanos Forskal)
+</t>
+  </si>
+  <si>
+    <t>Rekayasa Formulasi Kerupuk Ikan Berbasis Kombinasi Daging Lele (Clarias sp.) dan Tenggiri (Scomberomorus sp.) serta Implikasinya terhadap Sifat Fisik, Kimia, dan Sensorik Produk</t>
+  </si>
+  <si>
+    <t>Preparasi, Karakterisasi, dan Optimasi Ketebalan Lapisan Tunggal Bahan Non Magnetik Sekam Padi sebagai Radar Absorber Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengembangan Media Pembelajaran Fisika Berbasis Kerangka Kerja Deep Learning untuk Meningkatkan Minat Belajar dan Kemampuan Pemecahan Masalah Siswa
+</t>
+  </si>
+  <si>
+    <t>Pengaruh Pemberian Cat pada Atap Bangunan Terhadap Laju Transfer Panas</t>
+  </si>
+  <si>
+    <t>Rancang Bangun Prototype Alat Ukur Posisi Benda Berbasis Citra Stereoskopik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREDICTING CRYSTAL SYSTEMS OF LI-ION BATTERY CATHODES USING MACHINE LEARNING
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengembangan E-LKPD Berbasis Masalah Pokok Bahasan Pengukuran Besaran Fisis Untuk Meningkatkan Pemahanan Konsep dan Kemampuan Pengambilan Keputusan
+</t>
+  </si>
+  <si>
+    <t>Slamet Supriyadi REGULER ( PTH ) Margono; Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Ganjar Winasis REGULER ( DOSEN PEMULA ) Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Muhammad Amiruddin MANDIRI ( MANDIRI ) Imadudin Harjanto; Bambang Hadi Kunaryo; Affandi Faisal Kurniawan; Sigit Ristanto;</t>
+  </si>
+  <si>
+    <t>Rizky Muliani Dwi Ujianti REGULER - DASAR/FUNDAMENTAL ( REGULER - DASAR/FUNDAMENTAL ) Althesa Androva; Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Rizky Muliani Dwi Ujianti REGULER ( REG ) Althesa Androva; Bambang Hadi Kunaryo; Nur Aksin;</t>
+  </si>
+  <si>
+    <t>Adhi Kusmantoro PENELITIAN REGULER ( REGULER ) Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Agus Mukhtar REGULER ( DOSEN PEMULA ) Aan Burhanudin; Muhammad Amiruddin; Rifki Hermana;</t>
+  </si>
+  <si>
+    <t>Ikhwanudin PENELITIAN DESENTRALISASI ( PDUPT ) Farida Yudaningrum; Imadudin Harjanto;</t>
+  </si>
+  <si>
+    <t>Adhi Kusmantoro REGULER ( REG ) Irna Farikhah;</t>
+  </si>
+  <si>
+    <t>Adhi Kusmantoro  Irna Farikhah;</t>
+  </si>
+  <si>
+    <t>Achmad Buchori  Adhi Kusmantoro; Aan Burhanudin;</t>
+  </si>
+  <si>
+    <t>Irna Farikhah Harto Nuroso; Mega Novita;</t>
+  </si>
+  <si>
+    <t>Nur Khoiri Sigit Ristanto; Affandi Faisal Kurniawan;</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto Nur Khoiri; Affandi Faisal Kurniawan;</t>
+  </si>
+  <si>
+    <t>Sigit RistantoNur Khoiri; Affandi Faisal Kurniawan;</t>
+  </si>
+  <si>
+    <t>Mega Novita Sigit Ristanto; Ernawati Saptaningrum; Slamet Supriyadi;</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto Affandi Faisal Kurniawan; Ummi Kaltsum; Ernawati Saptaningrum;</t>
+  </si>
+  <si>
+    <t>Nur Khoiri Sapto Budoyo; Senowarsito; Sigit Ristanto;</t>
+  </si>
+  <si>
+    <t>Nur Khoiri Affandi Faisal Kurniawan; Joko Saefan;</t>
+  </si>
+  <si>
+    <t>Mega Novita Penelitian Kompetitif Nasional ( PFR )Rizky Muliani Dwi Ujianti; Affandi Faisal Kurniawan; Nur Latifah Dwi Mutiara Sari;</t>
+  </si>
+  <si>
+    <t>Affandi Faisal Kurniawan REGULER ( REGULER )Nur Khoiri; Joko Saefan;</t>
+  </si>
+  <si>
+    <t>IKHSAN SETIAWANAGUNG BAMBANG SETIO, PRASTOWO MURTI UTOMO, IRNA FARIKHAH</t>
+  </si>
+  <si>
+    <t>Irna FarikhahNur Khoiri, Setyoningsih Wibowo,</t>
+  </si>
+  <si>
+    <t>Dr SLAMET SUPRIYADI, M.Env.St.Margono, ST., M.Eng; Bambang Hadi Kunaryo, S.T., M.T.; Winda Margaretha; Silfia Dea Ananta; Sisilia Nava Brillian Angelica</t>
+  </si>
+  <si>
+    <t>Dr.Pi Rizky Muliani Dwi Ujianti, S.Pi., M.SiAlthesa Androva, S.T., M.Eng; Bambang Hadi Kunaryo, S.T., M.T.; CARISA ZAHRA AZURA; RIHMA NUR HAYATI; ALIFAH DWI SUSANTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Pi Rizky Muliani Dwi Ujianti, S.Pi., M.Si
+Althesa Androva, S.T., M.Eng; Bambang Hadi Kunaryo, S.T., M.T.; Nur Aksin, S.Ag., M.SI; KHOIRUS SA`ADAH; LAILATUS SA'DIYAH SEPTIYANI; MUTIARA SABATINA PUTRIYANTO
+</t>
+  </si>
+  <si>
+    <t>Dr.Pi Rizky Muliani Dwi Ujianti, S.Pi., M.SiAlthesa Androva, S.T., M.Eng; Bambang Hadi Kunaryo, S.T., M.T.; MUTIARA FITRI RAHMANINGTYAS; ARINA AINI NURUL KHASANAH; Abdillah Fathan Generus Annajah</t>
+  </si>
+  <si>
+    <t>Dr. Affandi Faisal Kurniawan, S.Si.,M.Sc.Prof. Dr. Nur Khoiri, S.Pd., M.T., M.Pd.; Dr. Sigit Ristanto, ST., M.Sc; Joko Saefan, M. Sc.; Naifah Istya Putri Aprilia; Nadroti Hidayatun Ni’mah; Murtiningsih</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sigit Ristanto, ST., M.Sc
+Prof. Dr. Nur Khoiri, S.Pd., M.T., M.Pd.; Dr. Affandi Faisal Kurniawan, S.Si.,M.Sc.; Emila Luthfia Sofa; Julia; Dwi Amiliya Putri
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sigit Ristanto, ST., M.ScDr SLAMET SUPRIYADI, M.Env.St.; Dr. Baju Arie Wibawa, S.T., M.T; Winda Margaretha; Yunita Dwi Saputri Ome; Pramudhita Alfina Damayanti
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Sigit Ristanto, ST., M.ScProf. Dr. Nur Khoiri, S.Pd., M.T., M.Pd.; Dr. Affandi Faisal Kurniawan, S.Si.,M.Sc.; Nur Roikhana Zulfa; Pramudhita Alfina Damayanti; Ratih Meiwulan
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr.Pi Rizky Muliani Dwi Ujianti, S.Pi., M.Si
+Dr. Sigit Ristanto, ST., M.Sc; Bambang Agus Herlambang, S.Kom., M.Kom; Rina Widyawati; Sri Wahyuni; Tri Ambarwati Mardikaningrum; Prof. Kazuyoshi Ogasawara
+</t>
+  </si>
+  <si>
+    <t> 2025  </t>
+  </si>
+  <si>
+    <t> 2024  </t>
+  </si>
+  <si>
+    <t> 2023  </t>
+  </si>
+  <si>
+    <t> 2021  </t>
+  </si>
+  <si>
+    <t> 2022  </t>
+  </si>
+  <si>
+    <t>Rp7,500,000.00</t>
+  </si>
+  <si>
+    <t>Rp10,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp5,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp9,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp90,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp6,500,000.00</t>
+  </si>
+  <si>
+    <t>Rp218,316,000.00</t>
+  </si>
+  <si>
+    <t>Rp20,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp99,664,000.00</t>
+  </si>
+  <si>
+    <t>Rp132,060,000.00</t>
+  </si>
+  <si>
+    <t>Rp24,500,000.00</t>
+  </si>
+  <si>
+    <t>Rp15,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp12,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp12,500,000.00</t>
+  </si>
+  <si>
+    <t>Rp23,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp50,000,000.00</t>
+  </si>
+  <si>
+    <t>LPPM</t>
+  </si>
+  <si>
+    <t>Mandiri</t>
+  </si>
+  <si>
+    <t>DRTPM</t>
+  </si>
+  <si>
+    <t>PENELITIAN KOMPETITIF NASIONAL ( PENELITIAN TERAPAN KOMPETITIF NASIONAL )</t>
+  </si>
+  <si>
+    <t>HIBAH APBU ( APBU )</t>
+  </si>
+  <si>
+    <t> PENELITIAN DESENTRALISASI ( PDUPT )</t>
+  </si>
+  <si>
+    <t>Penelitian Kompetitif Nasional ( PFR )</t>
+  </si>
+  <si>
+    <t>REGULER ( PTH )</t>
+  </si>
+  <si>
+    <t> REGULER ( REG )</t>
+  </si>
+  <si>
+    <t>KERJASAMA LUAR NEGERI ( KLN )</t>
+  </si>
+  <si>
+    <t>PENUGASAN ( PENUGASAN )</t>
+  </si>
+  <si>
+    <t>HIBAH APBU ( HIBAH APBU )</t>
+  </si>
+  <si>
+    <t>REGULER ( PTK )</t>
+  </si>
+  <si>
+    <t>lPPM</t>
+  </si>
+  <si>
+    <t>PROGRAM PENELITIAN INTERNAL 
+SKEMA KERJASAMA LUAR NEGERI</t>
+  </si>
+  <si>
+    <t>Reguler</t>
+  </si>
+  <si>
+    <t>PKM PROGRAM PERBAIKAN DAN EDUKASI PENGGUNAAN PERALATAN AUDIO BAGI PANTI ASUHAN FACHRUDIN SEMARANG</t>
+  </si>
+  <si>
+    <t>PKM KELOMPOK PEMBUDIDAYA LELE: TEKNOLOGI ZERO WASTE AIR LIMBAH KOLAM BERBASIS IOT UNTUK PENINGKATAN PRODUKSI DAN PENCEGAHAN STUNTING PADA ANAK</t>
+  </si>
+  <si>
+    <t>PKM PENDAMPINGAN INSTALASI SISTEM CCTV UNTUK MASJID BAITUL ROHMAH PUDAK PAYUNG SEMARANG</t>
+  </si>
+  <si>
+    <t>(PKM) PENDAMPINGAN PEMBENAHAN INSTALASI JARINGAN INTERNET LPQ ANNUR TANGGUL MAS BARAT SEMARANG</t>
+  </si>
+  <si>
+    <t>PENDAMPINGAN PEMBENAHAN INSTALASI KELISTRIKAN GENSET PANTI ASUHAN SULTAN FATAH NGALIYAN SEMARANG</t>
+  </si>
+  <si>
+    <t>SOSIALISASI UMKM TERKAIT INOVASI LABEL PEYEK</t>
+  </si>
+  <si>
+    <t>PENDAMPINGAN PENCEGAHAN WASPADA DEMAM BERDARAH</t>
+  </si>
+  <si>
+    <t>PENDAMPINGAN PENGENALAN TEKNOLOGI INFORMASI DAN KOMUNIKASI DALAM PEMASANG WIFI SETIAP WILAYAH KUPANG LOR AMBARAWA, KABUPATEN SEMARANG</t>
+  </si>
+  <si>
+    <t>Pemberdayaan Masyarakat Peternak Sapi Lokal Di Desa Kuripan Kecamatan Karangawen Kabupaten Demak Menuju Desa Sentra Energi Terbarukan</t>
+  </si>
+  <si>
+    <t>PELATIHAN MADING DIGITAL BERBASIS WEB BAGI KOMUNITAS SENI HYSTERIA SEMARANG</t>
+  </si>
+  <si>
+    <t>PKM BAGI SD NEGERI KALIBANTENG KULON 01 SEMARANG</t>
+  </si>
+  <si>
+    <t>PENGUATAN PEMBUATAN MEDIA PEMBELAJARAN INTERAKTIF BERBASIS IT MGMP IPA BLORA</t>
+  </si>
+  <si>
+    <t>PENGUATAN PEMBUATAN MEDIA PEMBELAJARAN INTERAKTIF BERBASIS IT MGMP IPA GROBOGAN</t>
+  </si>
+  <si>
+    <t>PKM MODEL PEMBELAJARAN BERBASIS DIGITAL BAGI GURU-GURU SMPN 3 SEMARANG</t>
+  </si>
+  <si>
+    <t>MEMBUAT MEDIA UNTUK POJOK BACA DI KABUPATEN KENDAL</t>
+  </si>
+  <si>
+    <t>PENGEDUKASIAN TERHADAP WARGA DESA LIMBANGAN, KENDAL UNTUK PEMANFAATAN LIMBAH ORGANIC MENJADI SABUN SERBA GUNA</t>
+  </si>
+  <si>
+    <t>PENGUATAN KARYA ILMIAH REMAJA (KIR) SISWA MAN 1 KOTA SEMARANG</t>
+  </si>
+  <si>
+    <t>PKM PENGUATAN PENYUSUNAN KARYA TULIS ILMIAH MGMP FISIKA KABUPATEN BOYOLALI</t>
+  </si>
+  <si>
+    <t>Bambang Hadi KunaryoGanjar Winasis; Afeef Kurnia Rahmawan;</t>
+  </si>
+  <si>
+    <t>Rizky Muliani Dwi Ujianti Setyoningsih Wibowo; Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Margono Imadudin Harjanto; Bambang Hadi Kunaryo;</t>
+  </si>
+  <si>
+    <t>Slamet Supriyadi Muhammad Amiruddin; Nur Aksin;</t>
+  </si>
+  <si>
+    <t>Margono Muhammad Amiruddin; Imadudin Harjanto;</t>
+  </si>
+  <si>
+    <t>Muhammad Amiruddin Personils : -</t>
+  </si>
+  <si>
+    <t>Muhammad AmiruddinPersonils : -</t>
+  </si>
+  <si>
+    <t>Achmad Buchori Suwarno Widodo; Siti Maisyaroh Bakti Pertiwi; Adhi Kusmantoro;</t>
+  </si>
+  <si>
+    <t>Theodora Indriati Wardani Adhi Kusmantoro; Irna Farikhah;</t>
+  </si>
+  <si>
+    <t>Adhi Kusmantoro Irna Farikhah; Theodora Indriati Wardani;</t>
+  </si>
+  <si>
+    <t>Affandi Faisal Kurniawan REGULER ( PKM-REGULER )Nur Khoiri; Sigit Ristanto;</t>
+  </si>
+  <si>
+    <t>Affandi Faisal Kurniawan PROGRAM KEMITRAAN MAYSARAKAT-REGULER ( PKM-REGULER )Nur Khoiri; Sigit Ristanto;</t>
+  </si>
+  <si>
+    <t>Maria Yosephine Widarti Lestari PROGRAM KEMITRAAN MAYSARAKAT-REGULER ( PKM-REGULER )Sigit Ristanto; Jafar Sodiq;</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto REGULER ( REG )Personils : -</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto PROGRAM KEMITRAAN MASYARAKAT-REGULER ( PKM-REG )Nur Khoiri; Affandi Faisal Kurniawan;</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto PROGRAM KEMITRAAN MAYSARAKAT-PENUGASAN ( PKM-PENUGASAN )Nur Khoiri; Affandi Faisal Kurniawan;</t>
+  </si>
+  <si>
+    <t>Rp8,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp44,500,000.00</t>
+  </si>
+  <si>
+    <t>Rp1,320,000.00</t>
+  </si>
+  <si>
+    <t>Rp1,760,000.00</t>
+  </si>
+  <si>
+    <t>Rp101,121,000.00</t>
+  </si>
+  <si>
+    <t>Rp5,750,000.00</t>
+  </si>
+  <si>
+    <t>Rp6,000,000.00</t>
+  </si>
+  <si>
+    <t>Rp1,650,000.00</t>
+  </si>
+  <si>
+    <t>Rp1,430,000.00</t>
+  </si>
+  <si>
+    <t>Rp14,000,000.00</t>
+  </si>
+  <si>
+    <t> REGULER ( PKM-REGULER )</t>
+  </si>
+  <si>
+    <t>KOMPETITIF NASIONAL ( PKM )</t>
+  </si>
+  <si>
+    <t>PROGRAM KEMITRAAN MASYARAKAT ( PKM )</t>
+  </si>
+  <si>
+    <t>MANDIRI ( PKM-MANDIRI )</t>
+  </si>
+  <si>
+    <t>PROGRAM KEMITRAAN MAYSARAKAT-REGULER ( PKM-REGULER )</t>
+  </si>
+  <si>
+    <t>REGULER ( REG )</t>
+  </si>
+  <si>
+    <t>Pengabdian Kepada Masyarakat Kompetitif Nasional ( PDB )</t>
   </si>
 </sst>
 </file>
@@ -1688,8 +2103,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2032,81 +2451,81 @@
         <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="C1" t="s">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="D1" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="E1" t="s">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="F1" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="G1" t="s">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="H1" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="I1" t="s">
-        <v>387</v>
+        <v>350</v>
       </c>
       <c r="J1" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="K1" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="L1" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="M1" t="s">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="N1" t="s">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="O1" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="P1" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="Q1" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="R1" t="s">
-        <v>396</v>
+        <v>359</v>
       </c>
       <c r="S1" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="B2" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="D2" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="E2" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="F2" t="s">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="G2" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="H2">
         <v>203</v>
@@ -2115,34 +2534,34 @@
         <v>3.32</v>
       </c>
       <c r="J2" t="s">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="K2" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="L2" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="M2" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="N2" t="s">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="O2" t="s">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="P2" t="s">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="s">
-        <v>412</v>
+        <v>375</v>
       </c>
       <c r="R2" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="S2" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -2163,19 +2582,19 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="D1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="G1" t="s">
-        <v>416</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2183,22 +2602,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="C2" t="s">
-        <v>418</v>
+        <v>381</v>
       </c>
       <c r="D2" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="G2" t="s">
-        <v>422</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2206,22 +2625,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>386</v>
       </c>
       <c r="C3" t="s">
-        <v>424</v>
+        <v>387</v>
       </c>
       <c r="D3" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="E3" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="F3" t="s">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="G3" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2229,22 +2648,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2252,22 +2671,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>397</v>
       </c>
       <c r="C5" t="s">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="D5" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="E5" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="G5" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2275,22 +2694,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="E6" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F6" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="G6" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -2308,31 +2727,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="C1" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="D1" t="s">
-        <v>445</v>
+        <v>408</v>
       </c>
       <c r="E1" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
       <c r="F1" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="I1" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="J1" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2340,31 +2759,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="C2" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="F2" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="G2" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="H2" t="s">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="I2" t="s">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="J2" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2372,31 +2791,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="D3" t="s">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="E3" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="F3" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="G3" t="s">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="I3" t="s">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="J3" t="s">
-        <v>467</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2404,31 +2823,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="D4" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="F4" t="s">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="H4" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="I4" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="J4" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2436,31 +2855,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="D5" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="E5" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="G5" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="H5" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="I5" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="J5" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2900,7 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2490,7 +2909,7 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>487</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2498,19 +2917,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="C2" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="D2" t="s">
-        <v>490</v>
+        <v>453</v>
       </c>
       <c r="E2" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F2" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2518,19 +2937,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="C3" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="D3" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="E3" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F3" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2538,19 +2957,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F4" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2558,19 +2977,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="C5" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="D5" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="E5" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2578,19 +2997,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="C6" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="D6" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="E6" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F6" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2598,19 +3017,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="C7" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="D7" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="E7" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F7" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2618,19 +3037,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="C8" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="D8" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="E8" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F8" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2638,19 +3057,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="C9" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="D9" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="E9" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F9" t="s">
-        <v>515</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2658,19 +3077,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>516</v>
+        <v>479</v>
       </c>
       <c r="C10" t="s">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="D10" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="E10" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F10" t="s">
-        <v>518</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2678,19 +3097,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="C11" t="s">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="D11" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
       <c r="E11" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="F11" t="s">
-        <v>522</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3187,6 +3606,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -3232,34 +3652,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C2" t="s">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
       </c>
       <c r="F2" t="s">
+        <v>502</v>
+      </c>
+      <c r="G2" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" t="s">
         <v>122</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>123</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>124</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>125</v>
-      </c>
-      <c r="J2" t="s">
-        <v>126</v>
-      </c>
-      <c r="L2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -3267,34 +3687,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="C3" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="D3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" t="s">
+        <v>502</v>
+      </c>
+      <c r="G3" t="s">
+        <v>510</v>
+      </c>
+      <c r="H3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I3" t="s">
         <v>129</v>
       </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J3" t="s">
-        <v>135</v>
-      </c>
       <c r="L3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -3302,34 +3722,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="C4" t="s">
-        <v>533</v>
+        <v>496</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" t="s">
-        <v>138</v>
+        <v>503</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>516</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -3337,34 +3754,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>489</v>
       </c>
       <c r="C5" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>504</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>511</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>516</v>
       </c>
       <c r="I5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="L5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -3372,34 +3789,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="C6" t="s">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>505</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>512</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="I6" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="L6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -3407,34 +3824,31 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>491</v>
       </c>
       <c r="C7" t="s">
-        <v>536</v>
+        <v>499</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="F7" t="s">
-        <v>156</v>
+        <v>506</v>
       </c>
       <c r="G7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" t="s">
-        <v>158</v>
+        <v>508</v>
       </c>
       <c r="I7" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="J7" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="L7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -3442,34 +3856,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>529</v>
+        <v>492</v>
       </c>
       <c r="C8" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>162</v>
+        <v>513</v>
       </c>
       <c r="H8" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I8" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="J8" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="L8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -3477,34 +3888,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="C9" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>507</v>
       </c>
       <c r="G9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" t="s">
-        <v>168</v>
+        <v>514</v>
       </c>
       <c r="I9" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="J9" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="L9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3522,22 +3930,22 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
         <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="F1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -3545,10 +3953,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -3557,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -3568,10 +3976,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -3580,10 +3988,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G3" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3591,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -3603,10 +4011,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -3614,10 +4022,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -3626,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3634,10 +4042,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -3646,10 +4054,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G6" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -3657,10 +4065,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -3669,10 +4077,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -3680,10 +4088,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -3692,10 +4100,10 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3703,10 +4111,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -3715,10 +4123,10 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G9" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3726,10 +4134,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -3738,10 +4146,10 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G10" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3749,10 +4157,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -3761,10 +4169,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G11" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3772,10 +4180,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -3784,7 +4192,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -3792,10 +4200,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -3804,10 +4212,10 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G13" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3815,10 +4223,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -3827,10 +4235,10 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G14" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -3838,10 +4246,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -3850,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G15" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -3861,10 +4269,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -3873,10 +4281,10 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -3884,10 +4292,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -3896,10 +4304,10 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -3907,10 +4315,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -3919,10 +4327,10 @@
         <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -3930,10 +4338,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -3942,10 +4350,10 @@
         <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G19" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -3953,10 +4361,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -3965,10 +4373,10 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -3976,10 +4384,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -3988,10 +4396,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -3999,10 +4407,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -4011,7 +4419,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -4019,10 +4427,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -4031,10 +4439,10 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G23" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -4042,10 +4450,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C24" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -4054,10 +4462,10 @@
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G24" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -4065,10 +4473,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C25" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -4077,10 +4485,10 @@
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G25" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -4088,10 +4496,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="C26" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -4100,10 +4508,10 @@
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G26" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -4111,10 +4519,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -4123,7 +4531,7 @@
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -4131,10 +4539,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C28" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -4143,10 +4551,10 @@
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -4154,10 +4562,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -4166,10 +4574,10 @@
         <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G29" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -4177,10 +4585,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -4189,10 +4597,10 @@
         <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -4200,10 +4608,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -4212,7 +4620,7 @@
         <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -4220,10 +4628,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -4232,10 +4640,10 @@
         <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G32" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -4243,10 +4651,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="C33" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -4255,10 +4663,10 @@
         <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G33" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -4266,10 +4674,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C34" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -4278,10 +4686,10 @@
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G34" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -4289,10 +4697,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C35" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -4301,10 +4709,10 @@
         <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G35" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -4312,10 +4720,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C36" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -4324,7 +4732,7 @@
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -4332,10 +4740,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C37" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4344,10 +4752,10 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="G37" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -4355,10 +4763,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -4367,7 +4775,7 @@
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4388,13 +4796,13 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4402,16 +4810,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4419,16 +4827,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="C3" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4436,16 +4844,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4453,16 +4861,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="D5" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4470,16 +4878,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4487,16 +4895,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4504,16 +4912,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="D8" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4521,16 +4929,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4538,16 +4946,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" t="s">
         <v>289</v>
       </c>
-      <c r="D10" t="s">
-        <v>309</v>
-      </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4555,16 +4963,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4572,16 +4980,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="D12" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4589,16 +4997,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E13" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4608,33 +5016,37 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.7265625" style="2"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="G1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="H1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -4647,119 +5059,1033 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>321</v>
+      <c r="B2" s="2" t="s">
+        <v>517</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>552</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>584</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>324</v>
+        <v>589</v>
       </c>
       <c r="G2" t="s">
-        <v>325</v>
-      </c>
-      <c r="H2" t="s">
-        <v>326</v>
-      </c>
-      <c r="I2" t="s">
-        <v>327</v>
-      </c>
-      <c r="J2" t="s">
-        <v>328</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>329</v>
+      <c r="B3" s="2" t="s">
+        <v>518</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>553</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>584</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>330</v>
+        <v>590</v>
       </c>
       <c r="G3" t="s">
-        <v>331</v>
-      </c>
-      <c r="H3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I3" t="s">
-        <v>333</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>334</v>
+      <c r="B4" s="2" t="s">
+        <v>519</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>554</v>
       </c>
       <c r="D4" t="s">
-        <v>335</v>
+        <v>585</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
-        <v>336</v>
-      </c>
       <c r="G4" t="s">
-        <v>325</v>
-      </c>
-      <c r="H4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" t="s">
-        <v>337</v>
-      </c>
-      <c r="J4" t="s">
-        <v>338</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>339</v>
+      <c r="B5" s="2" t="s">
+        <v>520</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>555</v>
       </c>
       <c r="D5" t="s">
-        <v>335</v>
+        <v>586</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
-        <v>340</v>
-      </c>
       <c r="G5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H5" t="s">
-        <v>341</v>
+        <v>605</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C6" t="s">
+        <v>556</v>
+      </c>
+      <c r="D6" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>591</v>
+      </c>
+      <c r="G6" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C7" t="s">
+        <v>557</v>
+      </c>
+      <c r="D7" t="s">
+        <v>584</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>592</v>
+      </c>
+      <c r="G7" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D8" t="s">
+        <v>586</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>593</v>
+      </c>
+      <c r="G8" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D9" t="s">
+        <v>585</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C10" t="s">
+        <v>560</v>
+      </c>
+      <c r="D10" t="s">
+        <v>586</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>595</v>
+      </c>
+      <c r="G10" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>596</v>
+      </c>
+      <c r="G11" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C12" t="s">
+        <v>562</v>
+      </c>
+      <c r="D12" t="s">
+        <v>588</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>597</v>
+      </c>
+      <c r="G12" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C13" t="s">
+        <v>563</v>
+      </c>
+      <c r="D13" t="s">
+        <v>584</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>597</v>
+      </c>
+      <c r="G13" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C14" t="s">
+        <v>564</v>
+      </c>
+      <c r="D14" t="s">
+        <v>584</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>597</v>
+      </c>
+      <c r="G14" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C15" t="s">
+        <v>565</v>
+      </c>
+      <c r="D15" t="s">
+        <v>585</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>597</v>
+      </c>
+      <c r="G15" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B16" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C16" t="s">
+        <v>566</v>
+      </c>
+      <c r="D16" t="s">
+        <v>586</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G16" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C17" t="s">
+        <v>567</v>
+      </c>
+      <c r="D17" t="s">
+        <v>586</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>597</v>
+      </c>
+      <c r="G17" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C18" t="s">
+        <v>568</v>
+      </c>
+      <c r="D18" t="s">
+        <v>586</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>597</v>
+      </c>
+      <c r="G18" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C19" t="s">
+        <v>564</v>
+      </c>
+      <c r="D19" t="s">
+        <v>586</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="s">
+        <v>597</v>
+      </c>
+      <c r="G19" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C20" t="s">
+        <v>564</v>
+      </c>
+      <c r="D20" t="s">
+        <v>588</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>597</v>
+      </c>
+      <c r="G20" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" t="s">
+        <v>569</v>
+      </c>
+      <c r="D21" t="s">
+        <v>588</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>597</v>
+      </c>
+      <c r="G21" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C22" t="s">
+        <v>564</v>
+      </c>
+      <c r="D22" t="s">
+        <v>584</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>597</v>
+      </c>
+      <c r="G22" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C23" t="s">
+        <v>570</v>
+      </c>
+      <c r="D23" t="s">
+        <v>585</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C24" t="s">
+        <v>571</v>
+      </c>
+      <c r="D24" t="s">
+        <v>585</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C25" t="s">
+        <v>572</v>
+      </c>
+      <c r="D25">
+        <v>2024</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C26" t="s">
+        <v>573</v>
+      </c>
+      <c r="D26">
+        <v>2025</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C27" t="s">
+        <v>574</v>
+      </c>
+      <c r="D27">
+        <v>2025</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" t="s">
+        <v>600</v>
+      </c>
+      <c r="G27" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C28" t="s">
+        <v>575</v>
+      </c>
+      <c r="D28">
+        <v>2024</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" t="s">
+        <v>601</v>
+      </c>
+      <c r="G28" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C29" t="s">
+        <v>576</v>
+      </c>
+      <c r="D29">
+        <v>2023</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
+        <v>601</v>
+      </c>
+      <c r="G29" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C30" t="s">
+        <v>577</v>
+      </c>
+      <c r="D30">
+        <v>2026</v>
+      </c>
+      <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
+        <v>602</v>
+      </c>
+      <c r="G30" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C31" t="s">
+        <v>578</v>
+      </c>
+      <c r="D31">
+        <v>2026</v>
+      </c>
+      <c r="E31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" t="s">
+        <v>602</v>
+      </c>
+      <c r="G31" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C32" t="s">
+        <v>579</v>
+      </c>
+      <c r="D32">
+        <v>2025</v>
+      </c>
+      <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
+        <v>600</v>
+      </c>
+      <c r="G32" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C33" t="s">
+        <v>580</v>
+      </c>
+      <c r="D33">
+        <v>2024</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
+        <v>603</v>
+      </c>
+      <c r="G33" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C34" t="s">
+        <v>581</v>
+      </c>
+      <c r="D34">
+        <v>2024</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" t="s">
+        <v>600</v>
+      </c>
+      <c r="G34" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="B35" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C35" t="s">
+        <v>582</v>
+      </c>
+      <c r="D35">
+        <v>2024</v>
+      </c>
+      <c r="E35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" t="s">
+        <v>604</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C36" t="s">
+        <v>583</v>
+      </c>
+      <c r="D36">
+        <v>2023</v>
+      </c>
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" t="s">
+        <v>590</v>
+      </c>
+      <c r="G36" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C37" t="s">
+        <v>639</v>
+      </c>
+      <c r="D37" t="s">
+        <v>584</v>
+      </c>
+      <c r="E37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" t="s">
+        <v>655</v>
+      </c>
+      <c r="G37" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C38" t="s">
+        <v>640</v>
+      </c>
+      <c r="D38" t="s">
+        <v>586</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>656</v>
+      </c>
+      <c r="G38" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C39" t="s">
+        <v>641</v>
+      </c>
+      <c r="D39" t="s">
+        <v>588</v>
+      </c>
+      <c r="E39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" t="s">
+        <v>655</v>
+      </c>
+      <c r="G39" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C40" t="s">
+        <v>642</v>
+      </c>
+      <c r="D40" t="s">
+        <v>584</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" t="s">
+        <v>590</v>
+      </c>
+      <c r="G40" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C41" t="s">
+        <v>643</v>
+      </c>
+      <c r="D41" t="s">
+        <v>586</v>
+      </c>
+      <c r="E41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>655</v>
+      </c>
+      <c r="G41" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C42" t="s">
+        <v>644</v>
+      </c>
+      <c r="D42" t="s">
+        <v>586</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" t="s">
+        <v>657</v>
+      </c>
+      <c r="G42" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C43" t="s">
+        <v>645</v>
+      </c>
+      <c r="D43" t="s">
+        <v>586</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" t="s">
+        <v>657</v>
+      </c>
+      <c r="G43" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C44" t="s">
+        <v>644</v>
+      </c>
+      <c r="D44" t="s">
+        <v>588</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" t="s">
+        <v>658</v>
+      </c>
+      <c r="G44" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C45" t="s">
+        <v>646</v>
+      </c>
+      <c r="D45" t="s">
+        <v>584</v>
+      </c>
+      <c r="E45" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" t="s">
+        <v>659</v>
+      </c>
+      <c r="G45" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C46" t="s">
+        <v>647</v>
+      </c>
+      <c r="D46" t="s">
+        <v>585</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" t="s">
+        <v>660</v>
+      </c>
+      <c r="G46" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C47" t="s">
+        <v>648</v>
+      </c>
+      <c r="D47" t="s">
+        <v>586</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>661</v>
+      </c>
+      <c r="G47" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C48" t="s">
+        <v>649</v>
+      </c>
+      <c r="D48" t="s">
+        <v>584</v>
+      </c>
+      <c r="E48" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B49" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C49" t="s">
+        <v>650</v>
+      </c>
+      <c r="D49" t="s">
+        <v>585</v>
+      </c>
+      <c r="E49" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B50" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C50" t="s">
+        <v>651</v>
+      </c>
+      <c r="D50" t="s">
+        <v>585</v>
+      </c>
+      <c r="E50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C51" t="s">
+        <v>652</v>
+      </c>
+      <c r="D51" t="s">
+        <v>586</v>
+      </c>
+      <c r="E51" t="s">
+        <v>40</v>
+      </c>
+      <c r="F51" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B52" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C52" t="s">
+        <v>652</v>
+      </c>
+      <c r="D52" t="s">
+        <v>586</v>
+      </c>
+      <c r="E52" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B53" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C53" t="s">
+        <v>653</v>
+      </c>
+      <c r="D53" t="s">
+        <v>586</v>
+      </c>
+      <c r="E53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B54" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C54" t="s">
+        <v>654</v>
+      </c>
+      <c r="D54" t="s">
+        <v>586</v>
+      </c>
+      <c r="E54" t="s">
+        <v>40</v>
+      </c>
+      <c r="F54" t="s">
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -4783,7 +6109,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -4795,7 +6121,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -4803,22 +6129,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>310</v>
       </c>
       <c r="G2" t="s">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="H2" t="s">
-        <v>349</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -4826,19 +6152,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -4846,19 +6172,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>318</v>
       </c>
       <c r="D4" t="s">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -4866,16 +6192,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -4883,19 +6209,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="D6" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>366</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4916,22 +6242,22 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="G1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="H1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -4945,31 +6271,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="E2" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="F2" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="G2" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>370</v>
+        <v>333</v>
       </c>
       <c r="I2" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="J2" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -4977,25 +6303,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="E3" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="F3" t="s">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="G3" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="H3" t="s">
-        <v>375</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -5003,28 +6329,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
         <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
-        <v>368</v>
+        <v>331</v>
       </c>
       <c r="F4" t="s">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="G4" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="H4" t="s">
-        <v>378</v>
+        <v>341</v>
       </c>
       <c r="I4" t="s">
-        <v>379</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
+++ b/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYDATA\Project\webte\te-upgris\src\data\dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC92D08F-DF86-436B-B2F6-880A07AE6576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F3723B-BC1E-4708-980A-0F239E2F503E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="beranda" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="606">
   <si>
     <t>videoUrl</t>
   </si>
@@ -502,322 +502,10 @@
     <t>rpsUrl</t>
   </si>
   <si>
-    <t>TE101</t>
-  </si>
-  <si>
-    <t>Matematika Teknik I</t>
-  </si>
-  <si>
-    <t>Pendukung</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_1</t>
-  </si>
-  <si>
-    <t>TE102</t>
-  </si>
-  <si>
-    <t>Fisika Teknik</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_2</t>
-  </si>
-  <si>
-    <t>TE103</t>
-  </si>
-  <si>
-    <t>Dasar Teknik Elektro</t>
-  </si>
-  <si>
-    <t>Kompetensi Utama</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_3</t>
-  </si>
-  <si>
-    <t>TE104</t>
-  </si>
-  <si>
-    <t>Kimia Teknik</t>
-  </si>
-  <si>
-    <t>TE105</t>
-  </si>
-  <si>
-    <t>Bahasa Indonesia Teknik</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_5</t>
-  </si>
-  <si>
-    <t>TE106</t>
-  </si>
-  <si>
-    <t>Pendidikan Agama</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_6</t>
-  </si>
-  <si>
-    <t>TE201</t>
-  </si>
-  <si>
-    <t>Matematika Teknik II</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_7</t>
-  </si>
-  <si>
-    <t>TE202</t>
-  </si>
-  <si>
-    <t>Rangkaian Listrik I</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_8</t>
-  </si>
-  <si>
-    <t>TE203</t>
-  </si>
-  <si>
-    <t>Elektronika I</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_9</t>
-  </si>
-  <si>
-    <t>TE204</t>
-  </si>
-  <si>
-    <t>Algoritma &amp; Pemrograman</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_10</t>
-  </si>
-  <si>
-    <t>TE205</t>
-  </si>
-  <si>
-    <t>Pancasila &amp; Kewarganegaraan</t>
-  </si>
-  <si>
-    <t>TE301</t>
-  </si>
-  <si>
-    <t>Rangkaian Listrik II</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_12</t>
-  </si>
-  <si>
-    <t>TE302</t>
-  </si>
-  <si>
-    <t>Elektronika II</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_13</t>
-  </si>
-  <si>
-    <t>TE303</t>
-  </si>
-  <si>
-    <t>Medan Elektromagnetik</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_14</t>
-  </si>
-  <si>
-    <t>TE304</t>
-  </si>
-  <si>
-    <t>Mesin Listrik I</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_15</t>
-  </si>
-  <si>
-    <t>TE305</t>
-  </si>
-  <si>
-    <t>Pengukuran &amp; Instrumentasi</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_16</t>
-  </si>
-  <si>
-    <t>TE401</t>
-  </si>
-  <si>
-    <t>Mesin Listrik II</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_17</t>
-  </si>
-  <si>
-    <t>TE402</t>
-  </si>
-  <si>
-    <t>Sistem Kontrol</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_18</t>
-  </si>
-  <si>
-    <t>TE403</t>
-  </si>
-  <si>
     <t>Elektronika Daya</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/dummy_rps_19</t>
-  </si>
-  <si>
-    <t>TE404</t>
-  </si>
-  <si>
-    <t>Mikrokontroler</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_20</t>
-  </si>
-  <si>
-    <t>TE405</t>
-  </si>
-  <si>
-    <t>Teknik Tegangan Tinggi</t>
-  </si>
-  <si>
-    <t>TE501</t>
-  </si>
-  <si>
-    <t>Sistem Tenaga Listrik</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_22</t>
-  </si>
-  <si>
-    <t>TE502</t>
-  </si>
-  <si>
-    <t>Sistem Telekomunikasi</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_23</t>
-  </si>
-  <si>
-    <t>TE503</t>
-  </si>
-  <si>
-    <t>PLC &amp; SCADA</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_24</t>
-  </si>
-  <si>
-    <t>TE504</t>
-  </si>
-  <si>
-    <t>Internet of Things</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_25</t>
-  </si>
-  <si>
-    <t>TE505</t>
-  </si>
-  <si>
-    <t>Kewirausahaan Teknik</t>
-  </si>
-  <si>
-    <t>TE601</t>
-  </si>
-  <si>
     <t>Energi Terbarukan</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_27</t>
-  </si>
-  <si>
-    <t>TE602</t>
-  </si>
-  <si>
-    <t>Robotika &amp; Otomasi Industri</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_28</t>
-  </si>
-  <si>
-    <t>TE603</t>
-  </si>
-  <si>
-    <t>Pemrosesan Sinyal Digital</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_29</t>
-  </si>
-  <si>
-    <t>TE604</t>
-  </si>
-  <si>
-    <t>Kerja Praktek</t>
-  </si>
-  <si>
-    <t>TE605</t>
-  </si>
-  <si>
-    <t>Metodologi Penelitian</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_31</t>
-  </si>
-  <si>
-    <t>TE701</t>
-  </si>
-  <si>
-    <t>Sistem Proteksi Tenaga Listrik</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_32</t>
-  </si>
-  <si>
-    <t>TE702</t>
-  </si>
-  <si>
-    <t>Konservasi &amp; Audit Energi</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_33</t>
-  </si>
-  <si>
-    <t>TE703</t>
-  </si>
-  <si>
-    <t>Kapstone Design I</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_34</t>
-  </si>
-  <si>
-    <t>TE704</t>
-  </si>
-  <si>
-    <t>Etika Profesi Insinyur</t>
-  </si>
-  <si>
-    <t>TE801</t>
-  </si>
-  <si>
-    <t>Kapstone Design II</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/dummy_rps_36</t>
-  </si>
-  <si>
-    <t>TE802</t>
-  </si>
-  <si>
-    <t>Skripsi</t>
   </si>
   <si>
     <t>jenis</t>
@@ -1563,6 +1251,9 @@
   </si>
   <si>
     <t>Konversi Energi</t>
+  </si>
+  <si>
+    <t>Pengolahan Citra</t>
   </si>
   <si>
     <t>Pembangkit Listrik Energi Terbarukan, Teknik Kontrol Digital, Metodologi Penelitian</t>
@@ -2068,13 +1759,124 @@
   </si>
   <si>
     <t>Pengabdian Kepada Masyarakat Kompetitif Nasional ( PDB )</t>
+  </si>
+  <si>
+    <t>Fisika Mekanika</t>
+  </si>
+  <si>
+    <t>MKW</t>
+  </si>
+  <si>
+    <t>Kalkulus</t>
+  </si>
+  <si>
+    <t>Fisika Listrik</t>
+  </si>
+  <si>
+    <t>Analisa Vektor</t>
+  </si>
+  <si>
+    <t>Fisika Modern</t>
+  </si>
+  <si>
+    <t>Perancangan Sistem Analog</t>
+  </si>
+  <si>
+    <t>MKK</t>
+  </si>
+  <si>
+    <t>Probabilitas Statistik</t>
+  </si>
+  <si>
+    <t>Isyarat dan Sistem</t>
+  </si>
+  <si>
+    <t>Komunikasi Data</t>
+  </si>
+  <si>
+    <t>Matematika Diskrit</t>
+  </si>
+  <si>
+    <t>Sistem Instrumentasi</t>
+  </si>
+  <si>
+    <t>Transmisi dan Distribusi</t>
+  </si>
+  <si>
+    <t>Variabel Kompleks</t>
+  </si>
+  <si>
+    <t>Dasar Sistem Kendali</t>
+  </si>
+  <si>
+    <t>Ke-PGRI-an</t>
+  </si>
+  <si>
+    <t>MKU</t>
+  </si>
+  <si>
+    <t>Komunikasi Nirkabel</t>
+  </si>
+  <si>
+    <t>Kuliah Kerja Lapangan (KKL)</t>
+  </si>
+  <si>
+    <t>Logika Fuzzy</t>
+  </si>
+  <si>
+    <t>Pengolahan Isyarat Digital</t>
+  </si>
+  <si>
+    <t>Sensor dan Tranduser</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris</t>
+  </si>
+  <si>
+    <t>Embeded System</t>
+  </si>
+  <si>
+    <t>Etika Profesi</t>
+  </si>
+  <si>
+    <t>Kecerdasan Buatan</t>
+  </si>
+  <si>
+    <t>Kewirausahaan berbasis Teknologi</t>
+  </si>
+  <si>
+    <t>Manajemen Proyek dan K3</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila</t>
+  </si>
+  <si>
+    <t>PLC</t>
+  </si>
+  <si>
+    <t>Antarmuka dan Arsitektur Komputer</t>
+  </si>
+  <si>
+    <t>Manajemen Energi dan sistem Hybrid</t>
+  </si>
+  <si>
+    <t>Manajemen Industri</t>
+  </si>
+  <si>
+    <t>Praktek Kerja Lapangan (PKL)</t>
+  </si>
+  <si>
+    <t>Rekayasa Teknik Elektro</t>
+  </si>
+  <si>
+    <t>Kuliah Kerja Nyata (KKN)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2082,16 +1884,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F7FA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE7F6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E5F5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3E0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7D6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2099,19 +1962,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{7F319157-8EBA-4E27-BD6D-ECC898A6892D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2451,81 +2380,81 @@
         <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="C1" t="s">
-        <v>344</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>345</v>
+        <v>241</v>
       </c>
       <c r="E1" t="s">
-        <v>346</v>
+        <v>242</v>
       </c>
       <c r="F1" t="s">
-        <v>347</v>
+        <v>243</v>
       </c>
       <c r="G1" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="H1" t="s">
-        <v>349</v>
+        <v>245</v>
       </c>
       <c r="I1" t="s">
-        <v>350</v>
+        <v>246</v>
       </c>
       <c r="J1" t="s">
-        <v>351</v>
+        <v>247</v>
       </c>
       <c r="K1" t="s">
-        <v>352</v>
+        <v>248</v>
       </c>
       <c r="L1" t="s">
-        <v>353</v>
+        <v>249</v>
       </c>
       <c r="M1" t="s">
-        <v>354</v>
+        <v>250</v>
       </c>
       <c r="N1" t="s">
-        <v>355</v>
+        <v>251</v>
       </c>
       <c r="O1" t="s">
-        <v>356</v>
+        <v>252</v>
       </c>
       <c r="P1" t="s">
-        <v>357</v>
+        <v>253</v>
       </c>
       <c r="Q1" t="s">
-        <v>358</v>
+        <v>254</v>
       </c>
       <c r="R1" t="s">
-        <v>359</v>
+        <v>255</v>
       </c>
       <c r="S1" t="s">
-        <v>360</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>362</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>363</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>364</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>365</v>
+        <v>261</v>
       </c>
       <c r="F2" t="s">
-        <v>366</v>
+        <v>262</v>
       </c>
       <c r="G2" t="s">
-        <v>367</v>
+        <v>263</v>
       </c>
       <c r="H2">
         <v>203</v>
@@ -2534,34 +2463,34 @@
         <v>3.32</v>
       </c>
       <c r="J2" t="s">
-        <v>368</v>
+        <v>264</v>
       </c>
       <c r="K2" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="L2" t="s">
-        <v>370</v>
+        <v>266</v>
       </c>
       <c r="M2" t="s">
-        <v>371</v>
+        <v>267</v>
       </c>
       <c r="N2" t="s">
-        <v>372</v>
+        <v>268</v>
       </c>
       <c r="O2" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="P2" t="s">
-        <v>374</v>
+        <v>270</v>
       </c>
       <c r="Q2" t="s">
-        <v>375</v>
+        <v>271</v>
       </c>
       <c r="R2" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
       <c r="S2" t="s">
-        <v>377</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2582,19 +2511,19 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="D1" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>378</v>
+        <v>274</v>
       </c>
       <c r="G1" t="s">
-        <v>379</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2602,22 +2531,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="D2" t="s">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="F2" t="s">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="G2" t="s">
-        <v>385</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2625,22 +2554,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>282</v>
       </c>
       <c r="C3" t="s">
-        <v>387</v>
+        <v>283</v>
       </c>
       <c r="D3" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="E3" t="s">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="G3" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2648,22 +2577,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>391</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>289</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F4" t="s">
-        <v>395</v>
+        <v>291</v>
       </c>
       <c r="G4" t="s">
-        <v>396</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2671,22 +2600,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>397</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>399</v>
+        <v>295</v>
       </c>
       <c r="E5" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F5" t="s">
-        <v>400</v>
+        <v>296</v>
       </c>
       <c r="G5" t="s">
-        <v>401</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2694,22 +2623,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>402</v>
+        <v>298</v>
       </c>
       <c r="C6" t="s">
-        <v>403</v>
+        <v>299</v>
       </c>
       <c r="D6" t="s">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="E6" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F6" t="s">
-        <v>404</v>
+        <v>300</v>
       </c>
       <c r="G6" t="s">
-        <v>405</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -2727,31 +2656,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>406</v>
+        <v>302</v>
       </c>
       <c r="C1" t="s">
-        <v>407</v>
+        <v>303</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>304</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>305</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>306</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>411</v>
+        <v>307</v>
       </c>
       <c r="I1" t="s">
-        <v>412</v>
+        <v>308</v>
       </c>
       <c r="J1" t="s">
-        <v>413</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2759,31 +2688,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>310</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>311</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>417</v>
+        <v>313</v>
       </c>
       <c r="F2" t="s">
-        <v>418</v>
+        <v>314</v>
       </c>
       <c r="G2" t="s">
-        <v>419</v>
+        <v>315</v>
       </c>
       <c r="H2" t="s">
-        <v>420</v>
+        <v>316</v>
       </c>
       <c r="I2" t="s">
-        <v>421</v>
+        <v>317</v>
       </c>
       <c r="J2" t="s">
-        <v>422</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2791,31 +2720,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>319</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
-        <v>424</v>
+        <v>320</v>
       </c>
       <c r="E3" t="s">
-        <v>425</v>
+        <v>321</v>
       </c>
       <c r="F3" t="s">
-        <v>426</v>
+        <v>322</v>
       </c>
       <c r="G3" t="s">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="H3" t="s">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="I3" t="s">
-        <v>429</v>
+        <v>325</v>
       </c>
       <c r="J3" t="s">
-        <v>430</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2823,31 +2752,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>433</v>
+        <v>329</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>330</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>331</v>
       </c>
       <c r="G4" t="s">
-        <v>436</v>
+        <v>332</v>
       </c>
       <c r="H4" t="s">
-        <v>437</v>
+        <v>333</v>
       </c>
       <c r="I4" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="J4" t="s">
-        <v>439</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2855,31 +2784,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>440</v>
+        <v>336</v>
       </c>
       <c r="C5" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="E5" t="s">
-        <v>443</v>
+        <v>339</v>
       </c>
       <c r="F5" t="s">
-        <v>444</v>
+        <v>340</v>
       </c>
       <c r="G5" t="s">
-        <v>445</v>
+        <v>341</v>
       </c>
       <c r="H5" t="s">
-        <v>446</v>
+        <v>342</v>
       </c>
       <c r="I5" t="s">
-        <v>447</v>
+        <v>343</v>
       </c>
       <c r="J5" t="s">
-        <v>448</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2829,7 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>449</v>
+        <v>345</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2909,7 +2838,7 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>450</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2917,19 +2846,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>451</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>452</v>
+        <v>348</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>349</v>
       </c>
       <c r="E2" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F2" t="s">
-        <v>454</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2937,19 +2866,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>455</v>
+        <v>351</v>
       </c>
       <c r="C3" t="s">
-        <v>456</v>
+        <v>352</v>
       </c>
       <c r="D3" t="s">
-        <v>457</v>
+        <v>353</v>
       </c>
       <c r="E3" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F3" t="s">
-        <v>458</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2957,19 +2886,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>459</v>
+        <v>355</v>
       </c>
       <c r="C4" t="s">
-        <v>460</v>
+        <v>356</v>
       </c>
       <c r="D4" t="s">
-        <v>457</v>
+        <v>353</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F4" t="s">
-        <v>461</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2977,19 +2906,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>462</v>
+        <v>358</v>
       </c>
       <c r="C5" t="s">
-        <v>463</v>
+        <v>359</v>
       </c>
       <c r="D5" t="s">
-        <v>457</v>
+        <v>353</v>
       </c>
       <c r="E5" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F5" t="s">
-        <v>464</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2997,19 +2926,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>465</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>466</v>
+        <v>362</v>
       </c>
       <c r="D6" t="s">
-        <v>467</v>
+        <v>363</v>
       </c>
       <c r="E6" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F6" t="s">
-        <v>468</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3017,19 +2946,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>469</v>
+        <v>365</v>
       </c>
       <c r="C7" t="s">
-        <v>470</v>
+        <v>366</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
+        <v>363</v>
       </c>
       <c r="E7" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F7" t="s">
-        <v>471</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -3037,19 +2966,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>472</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>473</v>
+        <v>369</v>
       </c>
       <c r="D8" t="s">
-        <v>467</v>
+        <v>363</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F8" t="s">
-        <v>474</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -3057,19 +2986,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>475</v>
+        <v>371</v>
       </c>
       <c r="C9" t="s">
-        <v>476</v>
+        <v>372</v>
       </c>
       <c r="D9" t="s">
-        <v>477</v>
+        <v>373</v>
       </c>
       <c r="E9" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F9" t="s">
-        <v>478</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3077,19 +3006,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>479</v>
+        <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>480</v>
+        <v>376</v>
       </c>
       <c r="D10" t="s">
-        <v>477</v>
+        <v>373</v>
       </c>
       <c r="E10" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F10" t="s">
-        <v>481</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3097,19 +3026,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>482</v>
+        <v>378</v>
       </c>
       <c r="C11" t="s">
-        <v>483</v>
+        <v>379</v>
       </c>
       <c r="D11" t="s">
-        <v>484</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="F11" t="s">
-        <v>485</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -3652,10 +3581,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>486</v>
+        <v>382</v>
       </c>
       <c r="C2" t="s">
-        <v>494</v>
+        <v>390</v>
       </c>
       <c r="D2" t="s">
         <v>127</v>
@@ -3664,10 +3593,10 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>502</v>
+        <v>398</v>
       </c>
       <c r="G2" t="s">
-        <v>509</v>
+        <v>406</v>
       </c>
       <c r="H2" t="s">
         <v>122</v>
@@ -3687,10 +3616,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>487</v>
+        <v>383</v>
       </c>
       <c r="C3" t="s">
-        <v>495</v>
+        <v>391</v>
       </c>
       <c r="D3" t="s">
         <v>127</v>
@@ -3699,13 +3628,13 @@
         <v>128</v>
       </c>
       <c r="F3" t="s">
-        <v>502</v>
+        <v>398</v>
       </c>
       <c r="G3" t="s">
-        <v>510</v>
+        <v>407</v>
       </c>
       <c r="H3" t="s">
-        <v>515</v>
+        <v>412</v>
       </c>
       <c r="I3" t="s">
         <v>129</v>
@@ -3722,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>488</v>
+        <v>384</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>392</v>
       </c>
       <c r="D4" t="s">
         <v>127</v>
@@ -3734,10 +3663,10 @@
         <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="H4" t="s">
-        <v>516</v>
+        <v>413</v>
       </c>
       <c r="I4" t="s">
         <v>132</v>
@@ -3754,10 +3683,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>489</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="D5" t="s">
         <v>127</v>
@@ -3766,13 +3695,13 @@
         <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>504</v>
+        <v>400</v>
       </c>
       <c r="G5" t="s">
-        <v>511</v>
+        <v>408</v>
       </c>
       <c r="H5" t="s">
-        <v>516</v>
+        <v>413</v>
       </c>
       <c r="I5" t="s">
         <v>135</v>
@@ -3789,10 +3718,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>490</v>
+        <v>386</v>
       </c>
       <c r="C6" t="s">
-        <v>498</v>
+        <v>394</v>
       </c>
       <c r="D6" t="s">
         <v>137</v>
@@ -3801,10 +3730,10 @@
         <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>505</v>
+        <v>401</v>
       </c>
       <c r="G6" t="s">
-        <v>512</v>
+        <v>409</v>
       </c>
       <c r="H6" t="s">
         <v>139</v>
@@ -3824,10 +3753,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>491</v>
+        <v>387</v>
       </c>
       <c r="C7" t="s">
-        <v>499</v>
+        <v>395</v>
       </c>
       <c r="D7" t="s">
         <v>137</v>
@@ -3836,10 +3765,10 @@
         <v>142</v>
       </c>
       <c r="F7" t="s">
-        <v>506</v>
+        <v>402</v>
       </c>
       <c r="G7" t="s">
-        <v>508</v>
+        <v>404</v>
       </c>
       <c r="I7" t="s">
         <v>143</v>
@@ -3856,10 +3785,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>492</v>
+        <v>388</v>
       </c>
       <c r="C8" t="s">
-        <v>500</v>
+        <v>396</v>
       </c>
       <c r="D8" t="s">
         <v>127</v>
@@ -3868,7 +3797,7 @@
         <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>513</v>
+        <v>410</v>
       </c>
       <c r="H8" t="s">
         <v>139</v>
@@ -3888,10 +3817,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>493</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s">
-        <v>501</v>
+        <v>397</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3900,10 +3829,10 @@
         <v>148</v>
       </c>
       <c r="F9" t="s">
-        <v>507</v>
+        <v>403</v>
       </c>
       <c r="G9" t="s">
-        <v>514</v>
+        <v>411</v>
       </c>
       <c r="I9" t="s">
         <v>149</v>
@@ -3922,7 +3851,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -3948,834 +3877,901 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="4">
+        <v>6625332615</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" t="s">
-        <v>159</v>
+      <c r="F2" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3">
+      <c r="B3" s="6">
+        <v>6625331620</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="D3" s="6">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F3" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="4">
+        <v>6625332616</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="D4" s="4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="8">
+        <v>6625331635</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="D5" s="8">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>158</v>
-      </c>
-      <c r="G6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="10">
+        <v>6625331617</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="10">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="G6" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="4">
+        <v>6625332650</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8">
+      <c r="B8" s="6">
+        <v>6625431653</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9">
+      <c r="B9" s="12">
+        <v>6625332610</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="12">
         <v>3</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>165</v>
-      </c>
-      <c r="G9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E9" s="12">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G9" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C10" t="s">
-        <v>182</v>
-      </c>
-      <c r="D10">
+      <c r="B10" s="14">
+        <v>6625331618</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="D10" s="14">
         <v>3</v>
       </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>165</v>
-      </c>
-      <c r="G10" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E10" s="14">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11">
+      <c r="B11" s="8">
+        <v>6625232625</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D11" s="8">
         <v>3</v>
       </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E11" s="8">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="16">
+        <v>6625331634</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="D12" s="16">
+        <v>3</v>
+      </c>
+      <c r="E12" s="16">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G12" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13">
+      <c r="B13" s="10">
+        <v>6625131657</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="D13" s="10">
         <v>3</v>
       </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E13" s="10">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G13" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>192</v>
-      </c>
-      <c r="C14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14">
+      <c r="B14" s="18">
+        <v>6625131660</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>582</v>
+      </c>
+      <c r="D14" s="18">
         <v>3</v>
       </c>
-      <c r="E14">
-        <v>3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>165</v>
-      </c>
-      <c r="G14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E14" s="18">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G14" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15">
+      <c r="B15" s="4">
+        <v>6625331636</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="D15" s="4">
         <v>3</v>
       </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15" t="s">
-        <v>165</v>
-      </c>
-      <c r="G15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E15" s="4">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D16">
+      <c r="B16" s="12">
+        <v>6625332606</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>584</v>
+      </c>
+      <c r="D16" s="12">
         <v>3</v>
       </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16" t="s">
-        <v>165</v>
-      </c>
-      <c r="G16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E16" s="12">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G16" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>165</v>
-      </c>
-      <c r="G17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="14">
+        <v>6625221622</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="8">
+        <v>6625322626</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="D18" s="8">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G18" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C19" t="s">
-        <v>208</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19" t="s">
-        <v>165</v>
-      </c>
-      <c r="G19" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="16">
+        <v>6625324628</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="D19" s="16">
+        <v>2</v>
+      </c>
+      <c r="E19" s="16">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G19" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20">
+      <c r="B20" s="10">
+        <v>6625332630</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="D20" s="10">
         <v>3</v>
       </c>
-      <c r="E20">
-        <v>4</v>
-      </c>
-      <c r="F20" t="s">
-        <v>165</v>
-      </c>
-      <c r="G20" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E20" s="10">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G20" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21">
+      <c r="B21" s="18">
+        <v>6625331649</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="D21" s="18">
         <v>3</v>
       </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21" t="s">
-        <v>165</v>
-      </c>
-      <c r="G21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E21" s="18">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G21" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22">
+      <c r="B22" s="4">
+        <v>6625331656</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="D22" s="4">
         <v>3</v>
       </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E22" s="4">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G22" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>218</v>
-      </c>
-      <c r="C23" t="s">
-        <v>219</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>165</v>
-      </c>
-      <c r="G23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="6">
+        <v>6625221605</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2</v>
+      </c>
+      <c r="E23" s="6">
+        <v>6</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G23" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C24" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24">
+      <c r="B24" s="12">
+        <v>6625332612</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D24" s="12">
         <v>3</v>
       </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>165</v>
-      </c>
-      <c r="G24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E24" s="12">
+        <v>6</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G24" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="14">
+        <v>6625321614</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14">
+        <v>6</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26">
+      <c r="B26" s="8">
+        <v>6625332623</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="D26" s="8">
         <v>3</v>
       </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>165</v>
-      </c>
-      <c r="G26" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E26" s="8">
+        <v>6</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G26" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>230</v>
-      </c>
-      <c r="C27" t="s">
-        <v>231</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="16">
+        <v>6625241624</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="D27" s="16">
+        <v>4</v>
+      </c>
+      <c r="E27" s="16">
+        <v>6</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G27" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>232</v>
-      </c>
-      <c r="C28" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
+      <c r="B28" s="10">
+        <v>6625321633</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2</v>
+      </c>
+      <c r="E28" s="10">
         <v>6</v>
       </c>
-      <c r="F28" t="s">
-        <v>165</v>
-      </c>
-      <c r="G28" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F28" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G28" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29" t="s">
-        <v>236</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29">
+      <c r="B29" s="18">
+        <v>6625321647</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="D29" s="18">
+        <v>2</v>
+      </c>
+      <c r="E29" s="18">
         <v>6</v>
       </c>
-      <c r="F29" t="s">
-        <v>165</v>
-      </c>
-      <c r="G29" t="s">
-        <v>237</v>
+      <c r="F29" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G29" s="18">
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>238</v>
-      </c>
-      <c r="C30" t="s">
-        <v>239</v>
-      </c>
-      <c r="D30">
+      <c r="B30" s="4">
+        <v>6625332651</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="D30" s="4">
         <v>3</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="4">
         <v>6</v>
       </c>
-      <c r="F30" t="s">
-        <v>165</v>
-      </c>
-      <c r="G30" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F30" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G30" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>241</v>
-      </c>
-      <c r="C31" t="s">
-        <v>242</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="6">
+        <v>6625322603</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="D31" s="6">
+        <v>3</v>
+      </c>
+      <c r="E31" s="6">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G31" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>243</v>
-      </c>
-      <c r="C32" t="s">
-        <v>244</v>
-      </c>
-      <c r="D32">
+      <c r="B32" s="12">
+        <v>6625421613</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="12">
         <v>2</v>
       </c>
-      <c r="E32">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>158</v>
-      </c>
-      <c r="G32" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E32" s="12">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G32" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C33" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33">
+      <c r="B33" s="14">
+        <v>6625422627</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="14">
         <v>7</v>
       </c>
-      <c r="F33" t="s">
-        <v>165</v>
-      </c>
-      <c r="G33" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F33" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" t="s">
-        <v>250</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
+      <c r="B34" s="8">
+        <v>6625421631</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="D34" s="8">
+        <v>2</v>
+      </c>
+      <c r="E34" s="8">
         <v>7</v>
       </c>
-      <c r="F34" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F34" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G34" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>252</v>
-      </c>
-      <c r="C35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35">
+      <c r="B35" s="16">
+        <v>6625421632</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D35" s="16">
+        <v>2</v>
+      </c>
+      <c r="E35" s="16">
         <v>7</v>
       </c>
-      <c r="F35" t="s">
-        <v>165</v>
-      </c>
-      <c r="G35" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F35" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G35" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>255</v>
-      </c>
-      <c r="C36" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36">
+      <c r="B36" s="10">
+        <v>6625322648</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D36" s="10">
         <v>2</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="10">
         <v>7</v>
       </c>
-      <c r="F36" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F36" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G36" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>257</v>
-      </c>
-      <c r="C37" t="s">
-        <v>258</v>
-      </c>
-      <c r="D37">
+      <c r="B37" s="18">
+        <v>6625745652</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="D37" s="18">
         <v>4</v>
       </c>
-      <c r="E37">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>165</v>
-      </c>
-      <c r="G37" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E37" s="18">
+        <v>7</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G37" s="18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>260</v>
-      </c>
-      <c r="C38" t="s">
-        <v>261</v>
-      </c>
-      <c r="D38">
+      <c r="B38" s="4">
+        <v>6625321638</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>7</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G38" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="12">
+        <v>6625244629</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="D39" s="12">
+        <v>4</v>
+      </c>
+      <c r="E39" s="12">
+        <v>8</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="G39" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14">
+        <v>6625765661</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D40" s="14">
         <v>6</v>
       </c>
-      <c r="E38">
+      <c r="E40" s="14">
         <v>8</v>
       </c>
-      <c r="F38" t="s">
-        <v>165</v>
+      <c r="F40" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="G40" s="14">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4796,13 +4792,13 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4810,16 +4806,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4827,16 +4823,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>268</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4844,16 +4840,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>273</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4861,16 +4857,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4878,16 +4874,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4895,16 +4891,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4912,16 +4908,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="E8" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4929,16 +4925,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>286</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4946,16 +4942,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>185</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4963,16 +4959,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="E11" t="s">
-        <v>277</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4980,16 +4976,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4997,16 +4993,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>295</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -5031,22 +5027,22 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="F1" t="s">
-        <v>298</v>
+        <v>194</v>
       </c>
       <c r="G1" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="H1" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -5056,471 +5052,531 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>517</v>
+        <v>414</v>
       </c>
       <c r="C2" t="s">
-        <v>552</v>
+        <v>449</v>
       </c>
       <c r="D2" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>589</v>
+        <v>486</v>
       </c>
       <c r="G2" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>518</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>553</v>
+        <v>450</v>
       </c>
       <c r="D3" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>590</v>
+        <v>487</v>
       </c>
       <c r="G3" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>519</v>
+        <v>416</v>
       </c>
       <c r="C4" t="s">
-        <v>554</v>
+        <v>451</v>
       </c>
       <c r="D4" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>520</v>
+        <v>417</v>
       </c>
       <c r="C5" t="s">
-        <v>555</v>
+        <v>452</v>
       </c>
       <c r="D5" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
       <c r="B6" s="2" t="s">
-        <v>521</v>
+        <v>418</v>
       </c>
       <c r="C6" t="s">
-        <v>556</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>587</v>
+        <v>484</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>591</v>
+        <v>488</v>
       </c>
       <c r="G6" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="2" t="s">
-        <v>522</v>
+        <v>419</v>
       </c>
       <c r="C7" t="s">
-        <v>557</v>
+        <v>454</v>
       </c>
       <c r="D7" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>592</v>
+        <v>489</v>
       </c>
       <c r="G7" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="2" t="s">
-        <v>523</v>
+        <v>420</v>
       </c>
       <c r="C8" t="s">
-        <v>558</v>
+        <v>455</v>
       </c>
       <c r="D8" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>593</v>
+        <v>490</v>
       </c>
       <c r="G8" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="2" t="s">
-        <v>524</v>
+        <v>421</v>
       </c>
       <c r="C9" t="s">
-        <v>559</v>
+        <v>456</v>
       </c>
       <c r="D9" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>594</v>
+        <v>491</v>
       </c>
       <c r="G9" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>525</v>
+        <v>422</v>
       </c>
       <c r="C10" t="s">
-        <v>560</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>595</v>
+        <v>492</v>
       </c>
       <c r="G10" t="s">
-        <v>608</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>526</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
-        <v>561</v>
+        <v>458</v>
       </c>
       <c r="D11" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>596</v>
+        <v>493</v>
       </c>
       <c r="G11" t="s">
-        <v>609</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="2" t="s">
-        <v>527</v>
+        <v>424</v>
       </c>
       <c r="C12" t="s">
-        <v>562</v>
+        <v>459</v>
       </c>
       <c r="D12" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G12" t="s">
-        <v>610</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>528</v>
+        <v>425</v>
       </c>
       <c r="C13" t="s">
-        <v>563</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G13" t="s">
-        <v>611</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="2" t="s">
-        <v>529</v>
+        <v>426</v>
       </c>
       <c r="C14" t="s">
-        <v>564</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G14" t="s">
-        <v>612</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="2" t="s">
-        <v>530</v>
+        <v>427</v>
       </c>
       <c r="C15" t="s">
-        <v>565</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G15" t="s">
-        <v>613</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="2" t="s">
-        <v>531</v>
+        <v>428</v>
       </c>
       <c r="C16" t="s">
-        <v>566</v>
+        <v>463</v>
       </c>
       <c r="D16" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G16" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="2" t="s">
-        <v>532</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>567</v>
+        <v>464</v>
       </c>
       <c r="D17" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G17" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>533</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>568</v>
+        <v>465</v>
       </c>
       <c r="D18" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G18" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="2" t="s">
-        <v>534</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>564</v>
+        <v>461</v>
       </c>
       <c r="D19" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G19" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="2" t="s">
-        <v>535</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>564</v>
+        <v>461</v>
       </c>
       <c r="D20" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G20" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
       <c r="B21" s="2" t="s">
-        <v>536</v>
+        <v>433</v>
       </c>
       <c r="C21" t="s">
-        <v>569</v>
+        <v>466</v>
       </c>
       <c r="D21" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G21" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
       <c r="B22" s="2" t="s">
-        <v>537</v>
+        <v>434</v>
       </c>
       <c r="C22" t="s">
-        <v>564</v>
+        <v>461</v>
       </c>
       <c r="D22" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G22" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
       <c r="B23" s="2" t="s">
-        <v>538</v>
+        <v>435</v>
       </c>
       <c r="C23" t="s">
-        <v>570</v>
+        <v>467</v>
       </c>
       <c r="D23" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
       <c r="B24" s="2" t="s">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="C24" t="s">
-        <v>571</v>
+        <v>468</v>
       </c>
       <c r="D24" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
       <c r="B25" s="2" t="s">
-        <v>540</v>
+        <v>437</v>
       </c>
       <c r="C25" t="s">
-        <v>572</v>
+        <v>469</v>
       </c>
       <c r="D25">
         <v>2024</v>
@@ -5529,15 +5585,18 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
       <c r="B26" s="2" t="s">
-        <v>541</v>
+        <v>438</v>
       </c>
       <c r="C26" t="s">
-        <v>573</v>
+        <v>470</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -5546,15 +5605,18 @@
         <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
       <c r="B27" s="2" t="s">
-        <v>542</v>
+        <v>439</v>
       </c>
       <c r="C27" t="s">
-        <v>574</v>
+        <v>471</v>
       </c>
       <c r="D27">
         <v>2025</v>
@@ -5563,18 +5625,21 @@
         <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>600</v>
+        <v>497</v>
       </c>
       <c r="G27" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>543</v>
+        <v>440</v>
       </c>
       <c r="C28" t="s">
-        <v>575</v>
+        <v>472</v>
       </c>
       <c r="D28">
         <v>2024</v>
@@ -5583,18 +5648,21 @@
         <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>601</v>
+        <v>498</v>
       </c>
       <c r="G28" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
       <c r="B29" s="2" t="s">
-        <v>544</v>
+        <v>441</v>
       </c>
       <c r="C29" t="s">
-        <v>576</v>
+        <v>473</v>
       </c>
       <c r="D29">
         <v>2023</v>
@@ -5603,18 +5671,21 @@
         <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>601</v>
+        <v>498</v>
       </c>
       <c r="G29" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
       <c r="B30" s="2" t="s">
-        <v>545</v>
+        <v>442</v>
       </c>
       <c r="C30" t="s">
-        <v>577</v>
+        <v>474</v>
       </c>
       <c r="D30">
         <v>2026</v>
@@ -5623,18 +5694,21 @@
         <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>602</v>
+        <v>499</v>
       </c>
       <c r="G30" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
       <c r="B31" s="2" t="s">
-        <v>546</v>
+        <v>443</v>
       </c>
       <c r="C31" t="s">
-        <v>578</v>
+        <v>475</v>
       </c>
       <c r="D31">
         <v>2026</v>
@@ -5643,18 +5717,21 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>602</v>
+        <v>499</v>
       </c>
       <c r="G31" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
       <c r="B32" s="2" t="s">
-        <v>547</v>
+        <v>444</v>
       </c>
       <c r="C32" t="s">
-        <v>579</v>
+        <v>476</v>
       </c>
       <c r="D32">
         <v>2025</v>
@@ -5663,18 +5740,21 @@
         <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>600</v>
+        <v>497</v>
       </c>
       <c r="G32" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
       <c r="B33" s="2" t="s">
-        <v>548</v>
+        <v>445</v>
       </c>
       <c r="C33" t="s">
-        <v>580</v>
+        <v>477</v>
       </c>
       <c r="D33">
         <v>2024</v>
@@ -5683,18 +5763,21 @@
         <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="G33" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
       <c r="B34" s="2" t="s">
-        <v>549</v>
+        <v>446</v>
       </c>
       <c r="C34" t="s">
-        <v>581</v>
+        <v>478</v>
       </c>
       <c r="D34">
         <v>2024</v>
@@ -5703,18 +5786,21 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>600</v>
+        <v>497</v>
       </c>
       <c r="G34" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="145" x14ac:dyDescent="0.35">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
       <c r="B35" s="2" t="s">
-        <v>550</v>
+        <v>447</v>
       </c>
       <c r="C35" t="s">
-        <v>582</v>
+        <v>479</v>
       </c>
       <c r="D35">
         <v>2024</v>
@@ -5723,18 +5809,21 @@
         <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>604</v>
+        <v>501</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
       <c r="B36" s="2" t="s">
-        <v>551</v>
+        <v>448</v>
       </c>
       <c r="C36" t="s">
-        <v>583</v>
+        <v>480</v>
       </c>
       <c r="D36">
         <v>2023</v>
@@ -5743,349 +5832,403 @@
         <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>590</v>
+        <v>487</v>
       </c>
       <c r="G36" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
       <c r="B37" s="2" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="C37" t="s">
-        <v>639</v>
+        <v>536</v>
       </c>
       <c r="D37" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E37" t="s">
         <v>40</v>
       </c>
       <c r="F37" t="s">
-        <v>655</v>
+        <v>552</v>
       </c>
       <c r="G37" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
       <c r="B38" s="2" t="s">
-        <v>622</v>
+        <v>519</v>
       </c>
       <c r="C38" t="s">
-        <v>640</v>
+        <v>537</v>
       </c>
       <c r="D38" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E38" t="s">
         <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>656</v>
+        <v>553</v>
       </c>
       <c r="G38" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
       <c r="B39" s="2" t="s">
-        <v>623</v>
+        <v>520</v>
       </c>
       <c r="C39" t="s">
-        <v>641</v>
+        <v>538</v>
       </c>
       <c r="D39" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E39" t="s">
         <v>40</v>
       </c>
       <c r="F39" t="s">
-        <v>655</v>
+        <v>552</v>
       </c>
       <c r="G39" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
       <c r="B40" s="2" t="s">
-        <v>624</v>
+        <v>521</v>
       </c>
       <c r="C40" t="s">
-        <v>642</v>
+        <v>539</v>
       </c>
       <c r="D40" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E40" t="s">
         <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>590</v>
+        <v>487</v>
       </c>
       <c r="G40" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
       <c r="B41" s="2" t="s">
-        <v>625</v>
+        <v>522</v>
       </c>
       <c r="C41" t="s">
-        <v>643</v>
+        <v>540</v>
       </c>
       <c r="D41" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>655</v>
+        <v>552</v>
       </c>
       <c r="G41" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
       <c r="B42" s="2" t="s">
-        <v>626</v>
+        <v>523</v>
       </c>
       <c r="C42" t="s">
-        <v>644</v>
+        <v>541</v>
       </c>
       <c r="D42" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E42" t="s">
         <v>40</v>
       </c>
       <c r="F42" t="s">
-        <v>657</v>
+        <v>554</v>
       </c>
       <c r="G42" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
       <c r="B43" s="2" t="s">
-        <v>627</v>
+        <v>524</v>
       </c>
       <c r="C43" t="s">
-        <v>645</v>
+        <v>542</v>
       </c>
       <c r="D43" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E43" t="s">
         <v>40</v>
       </c>
       <c r="F43" t="s">
-        <v>657</v>
+        <v>554</v>
       </c>
       <c r="G43" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
       <c r="B44" s="2" t="s">
-        <v>628</v>
+        <v>525</v>
       </c>
       <c r="C44" t="s">
-        <v>644</v>
+        <v>541</v>
       </c>
       <c r="D44" t="s">
-        <v>588</v>
+        <v>485</v>
       </c>
       <c r="E44" t="s">
         <v>40</v>
       </c>
       <c r="F44" t="s">
-        <v>658</v>
+        <v>555</v>
       </c>
       <c r="G44" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
       <c r="B45" s="2" t="s">
-        <v>629</v>
+        <v>526</v>
       </c>
       <c r="C45" t="s">
-        <v>646</v>
+        <v>543</v>
       </c>
       <c r="D45" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E45" t="s">
         <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>659</v>
+        <v>556</v>
       </c>
       <c r="G45" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
       <c r="B46" s="2" t="s">
-        <v>630</v>
+        <v>527</v>
       </c>
       <c r="C46" t="s">
-        <v>647</v>
+        <v>544</v>
       </c>
       <c r="D46" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E46" t="s">
         <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>660</v>
+        <v>557</v>
       </c>
       <c r="G46" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
       <c r="B47" s="2" t="s">
-        <v>631</v>
+        <v>528</v>
       </c>
       <c r="C47" t="s">
-        <v>648</v>
+        <v>545</v>
       </c>
       <c r="D47" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E47" t="s">
         <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>661</v>
+        <v>558</v>
       </c>
       <c r="G47" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
       <c r="B48" s="2" t="s">
-        <v>632</v>
+        <v>529</v>
       </c>
       <c r="C48" t="s">
-        <v>649</v>
+        <v>546</v>
       </c>
       <c r="D48" t="s">
-        <v>584</v>
+        <v>481</v>
       </c>
       <c r="E48" t="s">
         <v>40</v>
       </c>
       <c r="F48" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
       <c r="B49" s="2" t="s">
-        <v>633</v>
+        <v>530</v>
       </c>
       <c r="C49" t="s">
-        <v>650</v>
+        <v>547</v>
       </c>
       <c r="D49" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E49" t="s">
         <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
       <c r="B50" s="2" t="s">
-        <v>634</v>
+        <v>531</v>
       </c>
       <c r="C50" t="s">
-        <v>651</v>
+        <v>548</v>
       </c>
       <c r="D50" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="E50" t="s">
         <v>40</v>
       </c>
       <c r="F50" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
       <c r="B51" s="2" t="s">
-        <v>635</v>
+        <v>532</v>
       </c>
       <c r="C51" t="s">
-        <v>652</v>
+        <v>549</v>
       </c>
       <c r="D51" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E51" t="s">
         <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
       <c r="B52" s="2" t="s">
-        <v>636</v>
+        <v>533</v>
       </c>
       <c r="C52" t="s">
-        <v>652</v>
+        <v>549</v>
       </c>
       <c r="D52" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E52" t="s">
         <v>40</v>
       </c>
       <c r="F52" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
       <c r="B53" s="2" t="s">
-        <v>637</v>
+        <v>534</v>
       </c>
       <c r="C53" t="s">
-        <v>653</v>
+        <v>550</v>
       </c>
       <c r="D53" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E53" t="s">
         <v>40</v>
       </c>
       <c r="F53" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
       <c r="B54" s="2" t="s">
-        <v>638</v>
+        <v>535</v>
       </c>
       <c r="C54" t="s">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="D54" t="s">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="E54" t="s">
         <v>40</v>
       </c>
       <c r="F54" t="s">
-        <v>664</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -6109,7 +6252,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -6121,7 +6264,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>306</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -6129,22 +6272,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="G2" t="s">
-        <v>311</v>
+        <v>207</v>
       </c>
       <c r="H2" t="s">
-        <v>312</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -6152,19 +6295,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>210</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>316</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -6172,19 +6315,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>214</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>320</v>
+        <v>216</v>
       </c>
       <c r="G4" t="s">
-        <v>321</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -6192,16 +6335,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>325</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -6209,19 +6352,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>224</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>329</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6242,22 +6385,22 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="F1" t="s">
-        <v>298</v>
+        <v>194</v>
       </c>
       <c r="G1" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="H1" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -6271,31 +6414,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="F2" t="s">
-        <v>332</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="H2" t="s">
-        <v>333</v>
+        <v>229</v>
       </c>
       <c r="I2" t="s">
-        <v>334</v>
+        <v>230</v>
       </c>
       <c r="J2" t="s">
-        <v>335</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -6303,25 +6446,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
         <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="E3" t="s">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="F3" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="G3" t="s">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="H3" t="s">
-        <v>338</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -6329,28 +6472,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>339</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
         <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
-        <v>340</v>
+        <v>236</v>
       </c>
       <c r="G4" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="H4" t="s">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="I4" t="s">
-        <v>342</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
+++ b/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYDATA\Project\webte\te-upgris\src\data\dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F3723B-BC1E-4708-980A-0F239E2F503E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1FD21A-0C9E-4EE7-AA44-96CC1C10532B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="beranda" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="594">
   <si>
     <t>videoUrl</t>
   </si>
@@ -412,9 +412,6 @@
     <t>DTPS</t>
   </si>
   <si>
-    <t>Ir. Budi Hartono, S.T., M.Eng.</t>
-  </si>
-  <si>
     <t>Lektor</t>
   </si>
   <si>
@@ -625,18 +622,6 @@
     <t>roadmap</t>
   </si>
   <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>Dikti</t>
-  </si>
-  <si>
-    <t>Internal Lembaga</t>
-  </si>
-  <si>
-    <t>TS-1</t>
-  </si>
-  <si>
     <t>deskripsi</t>
   </si>
   <si>
@@ -712,15 +697,6 @@
     <t>https://drive.google.com/file/d/dummy_form_kp</t>
   </si>
   <si>
-    <t>Instalasi Panel Surya &amp; Pelatihan Energi Terbarukan untuk UMKM Semarang Tengah</t>
-  </si>
-  <si>
-    <t>PkM</t>
-  </si>
-  <si>
-    <t>Rp 30.000.000</t>
-  </si>
-  <si>
     <t>Energi Terbarukan Komunitas</t>
   </si>
   <si>
@@ -730,19 +706,7 @@
     <t>/content/pkm/pkm-1.md</t>
   </si>
   <si>
-    <t>Pelatihan Programmable Logic Controller (PLC) untuk Teknisi Industri Jawa Tengah</t>
-  </si>
-  <si>
-    <t>Rp 25.000.000</t>
-  </si>
-  <si>
     <t>Literasi Teknologi Industri</t>
-  </si>
-  <si>
-    <t>Pendampingan Elektrifikasi Rumah Adat di Desa Wisata Kabupaten Semarang</t>
-  </si>
-  <si>
-    <t>Rp 20.000.000</t>
   </si>
   <si>
     <t>Elektrifikasi Pedesaan</t>
@@ -2380,81 +2344,81 @@
         <v>110</v>
       </c>
       <c r="B1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N1" t="s">
         <v>239</v>
       </c>
-      <c r="C1" t="s">
+      <c r="O1" t="s">
         <v>240</v>
       </c>
-      <c r="D1" t="s">
+      <c r="P1" t="s">
         <v>241</v>
       </c>
-      <c r="E1" t="s">
+      <c r="Q1" t="s">
         <v>242</v>
       </c>
-      <c r="F1" t="s">
+      <c r="R1" t="s">
         <v>243</v>
       </c>
-      <c r="G1" t="s">
+      <c r="S1" t="s">
         <v>244</v>
-      </c>
-      <c r="H1" t="s">
-        <v>245</v>
-      </c>
-      <c r="I1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M1" t="s">
-        <v>250</v>
-      </c>
-      <c r="N1" t="s">
-        <v>251</v>
-      </c>
-      <c r="O1" t="s">
-        <v>252</v>
-      </c>
-      <c r="P1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>254</v>
-      </c>
-      <c r="R1" t="s">
-        <v>255</v>
-      </c>
-      <c r="S1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="G2" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2">
         <v>203</v>
@@ -2463,34 +2427,34 @@
         <v>3.32</v>
       </c>
       <c r="J2" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="K2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="L2" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="M2" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="N2" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="O2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="Q2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="R2" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="S2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2511,19 +2475,19 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E1" t="s">
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="G1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2531,22 +2495,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="F2" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2554,22 +2518,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="F3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="G3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2577,22 +2541,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="G4" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2600,22 +2564,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F5" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G5" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2623,22 +2587,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" t="s">
         <v>278</v>
       </c>
-      <c r="E6" t="s">
-        <v>290</v>
-      </c>
       <c r="F6" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="G6" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2656,31 +2620,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C1" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D1" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="F1" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="I1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="J1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2688,31 +2652,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="F2" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="G2" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="I2" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2720,31 +2684,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" t="s">
         <v>311</v>
       </c>
-      <c r="D3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" t="s">
-        <v>321</v>
-      </c>
-      <c r="F3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G3" t="s">
-        <v>323</v>
-      </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="I3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="J3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2752,31 +2716,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E4" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="F4" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="G4" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="I4" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="J4" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2784,31 +2748,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F5" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="G5" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="H5" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="I5" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="J5" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -2829,7 +2793,7 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2838,7 +2802,7 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2846,19 +2810,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F2" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2866,19 +2830,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2886,19 +2850,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F4" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2906,19 +2870,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F5" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2926,19 +2890,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="C6" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D6" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2946,19 +2910,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D7" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F7" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2966,19 +2930,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C8" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="E8" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F8" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2986,19 +2950,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C9" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D9" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F9" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3006,19 +2970,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C10" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D10" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3026,19 +2990,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F11" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -3581,22 +3545,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C2" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="H2" t="s">
         <v>122</v>
@@ -3616,31 +3580,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
         <v>127</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>386</v>
+      </c>
+      <c r="G3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I3" t="s">
         <v>128</v>
       </c>
-      <c r="F3" t="s">
-        <v>398</v>
-      </c>
-      <c r="G3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>129</v>
-      </c>
-      <c r="J3" t="s">
-        <v>130</v>
       </c>
       <c r="L3" t="s">
         <v>125</v>
@@ -3651,28 +3615,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" t="s">
+        <v>401</v>
+      </c>
+      <c r="I4" t="s">
         <v>131</v>
       </c>
-      <c r="F4" t="s">
-        <v>399</v>
-      </c>
-      <c r="H4" t="s">
-        <v>413</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>132</v>
-      </c>
-      <c r="J4" t="s">
-        <v>133</v>
       </c>
       <c r="L4" t="s">
         <v>125</v>
@@ -3683,31 +3647,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C5" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" t="s">
+        <v>388</v>
+      </c>
+      <c r="G5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H5" t="s">
+        <v>401</v>
+      </c>
+      <c r="I5" t="s">
         <v>134</v>
       </c>
-      <c r="F5" t="s">
-        <v>400</v>
-      </c>
-      <c r="G5" t="s">
-        <v>408</v>
-      </c>
-      <c r="H5" t="s">
-        <v>413</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>135</v>
-      </c>
-      <c r="J5" t="s">
-        <v>136</v>
       </c>
       <c r="L5" t="s">
         <v>125</v>
@@ -3718,31 +3682,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="C6" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" t="s">
         <v>137</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>389</v>
+      </c>
+      <c r="G6" t="s">
+        <v>397</v>
+      </c>
+      <c r="H6" t="s">
         <v>138</v>
       </c>
-      <c r="F6" t="s">
-        <v>401</v>
-      </c>
-      <c r="G6" t="s">
-        <v>409</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>139</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>140</v>
-      </c>
-      <c r="J6" t="s">
-        <v>141</v>
       </c>
       <c r="L6" t="s">
         <v>125</v>
@@ -3753,28 +3717,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G7" t="s">
+        <v>392</v>
+      </c>
+      <c r="I7" t="s">
         <v>142</v>
       </c>
-      <c r="F7" t="s">
-        <v>402</v>
-      </c>
-      <c r="G7" t="s">
-        <v>404</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>143</v>
-      </c>
-      <c r="J7" t="s">
-        <v>144</v>
       </c>
       <c r="L7" t="s">
         <v>125</v>
@@ -3785,28 +3749,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" t="s">
         <v>145</v>
       </c>
-      <c r="G8" t="s">
-        <v>410</v>
-      </c>
-      <c r="H8" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>146</v>
-      </c>
-      <c r="J8" t="s">
-        <v>147</v>
       </c>
       <c r="L8" t="s">
         <v>125</v>
@@ -3817,28 +3781,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
       </c>
       <c r="E9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" t="s">
+        <v>391</v>
+      </c>
+      <c r="G9" t="s">
+        <v>399</v>
+      </c>
+      <c r="I9" t="s">
         <v>148</v>
       </c>
-      <c r="F9" t="s">
-        <v>403</v>
-      </c>
-      <c r="G9" t="s">
-        <v>411</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>149</v>
-      </c>
-      <c r="J9" t="s">
-        <v>150</v>
       </c>
       <c r="L9" t="s">
         <v>125</v>
@@ -3859,22 +3823,22 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C1" t="s">
         <v>110</v>
       </c>
       <c r="D1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" t="s">
         <v>152</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>153</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>154</v>
-      </c>
-      <c r="G1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
@@ -3885,7 +3849,7 @@
         <v>6625332615</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="D2" s="4">
         <v>3</v>
@@ -3894,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -3908,7 +3872,7 @@
         <v>6625331620</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="D3" s="6">
         <v>3</v>
@@ -3917,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G3" s="6">
         <v>1</v>
@@ -3931,7 +3895,7 @@
         <v>6625332616</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
@@ -3940,7 +3904,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -3954,7 +3918,7 @@
         <v>6625331635</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -3963,7 +3927,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G5" s="8">
         <v>3</v>
@@ -3977,7 +3941,7 @@
         <v>6625331617</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="D6" s="10">
         <v>3</v>
@@ -3986,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G6" s="10">
         <v>3</v>
@@ -4000,7 +3964,7 @@
         <v>6625332650</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
@@ -4009,7 +3973,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -4023,7 +3987,7 @@
         <v>6625431653</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D8" s="6">
         <v>3</v>
@@ -4032,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G8" s="6">
         <v>3</v>
@@ -4046,7 +4010,7 @@
         <v>6625332610</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D9" s="12">
         <v>3</v>
@@ -4055,7 +4019,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G9" s="12">
         <v>4</v>
@@ -4069,7 +4033,7 @@
         <v>6625331618</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="D10" s="14">
         <v>3</v>
@@ -4078,7 +4042,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G10" s="14">
         <v>4</v>
@@ -4092,7 +4056,7 @@
         <v>6625232625</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="D11" s="8">
         <v>3</v>
@@ -4101,7 +4065,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G11" s="8">
         <v>4</v>
@@ -4115,7 +4079,7 @@
         <v>6625331634</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="D12" s="16">
         <v>3</v>
@@ -4124,7 +4088,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G12" s="16">
         <v>4</v>
@@ -4138,7 +4102,7 @@
         <v>6625131657</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="D13" s="10">
         <v>3</v>
@@ -4147,7 +4111,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G13" s="10">
         <v>4</v>
@@ -4161,7 +4125,7 @@
         <v>6625131660</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="D14" s="18">
         <v>3</v>
@@ -4170,7 +4134,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G14" s="18">
         <v>4</v>
@@ -4184,7 +4148,7 @@
         <v>6625331636</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
@@ -4193,7 +4157,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G15" s="4">
         <v>4</v>
@@ -4207,7 +4171,7 @@
         <v>6625332606</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="D16" s="12">
         <v>3</v>
@@ -4216,7 +4180,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G16" s="12">
         <v>5</v>
@@ -4230,7 +4194,7 @@
         <v>6625221622</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
@@ -4239,7 +4203,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G17" s="14">
         <v>5</v>
@@ -4253,7 +4217,7 @@
         <v>6625322626</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="D18" s="8">
         <v>2</v>
@@ -4262,7 +4226,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G18" s="8">
         <v>5</v>
@@ -4276,7 +4240,7 @@
         <v>6625324628</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="D19" s="16">
         <v>2</v>
@@ -4285,7 +4249,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G19" s="16">
         <v>5</v>
@@ -4299,7 +4263,7 @@
         <v>6625332630</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="D20" s="10">
         <v>3</v>
@@ -4308,7 +4272,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G20" s="10">
         <v>5</v>
@@ -4322,7 +4286,7 @@
         <v>6625331649</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D21" s="18">
         <v>3</v>
@@ -4331,7 +4295,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G21" s="18">
         <v>5</v>
@@ -4345,7 +4309,7 @@
         <v>6625331656</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -4354,7 +4318,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G22" s="4">
         <v>5</v>
@@ -4368,7 +4332,7 @@
         <v>6625221605</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
@@ -4377,7 +4341,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G23" s="6">
         <v>6</v>
@@ -4391,7 +4355,7 @@
         <v>6625332612</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="D24" s="12">
         <v>3</v>
@@ -4400,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G24" s="12">
         <v>6</v>
@@ -4414,7 +4378,7 @@
         <v>6625321614</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -4423,7 +4387,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
@@ -4437,7 +4401,7 @@
         <v>6625332623</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="D26" s="8">
         <v>3</v>
@@ -4446,7 +4410,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G26" s="8">
         <v>6</v>
@@ -4460,7 +4424,7 @@
         <v>6625241624</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D27" s="16">
         <v>4</v>
@@ -4469,7 +4433,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G27" s="16">
         <v>6</v>
@@ -4483,7 +4447,7 @@
         <v>6625321633</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="D28" s="10">
         <v>2</v>
@@ -4492,7 +4456,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G28" s="10">
         <v>6</v>
@@ -4506,7 +4470,7 @@
         <v>6625321647</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D29" s="18">
         <v>2</v>
@@ -4515,7 +4479,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G29" s="18">
         <v>6</v>
@@ -4529,7 +4493,7 @@
         <v>6625332651</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="D30" s="4">
         <v>3</v>
@@ -4538,7 +4502,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G30" s="4">
         <v>6</v>
@@ -4552,7 +4516,7 @@
         <v>6625322603</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D31" s="6">
         <v>3</v>
@@ -4561,7 +4525,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G31" s="6">
         <v>7</v>
@@ -4575,7 +4539,7 @@
         <v>6625421613</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D32" s="12">
         <v>2</v>
@@ -4584,7 +4548,7 @@
         <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G32" s="12">
         <v>7</v>
@@ -4598,7 +4562,7 @@
         <v>6625422627</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -4607,7 +4571,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G33" s="14">
         <v>7</v>
@@ -4621,7 +4585,7 @@
         <v>6625421631</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="D34" s="8">
         <v>2</v>
@@ -4630,7 +4594,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G34" s="8">
         <v>7</v>
@@ -4644,7 +4608,7 @@
         <v>6625421632</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D35" s="16">
         <v>2</v>
@@ -4653,7 +4617,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G35" s="16">
         <v>7</v>
@@ -4667,7 +4631,7 @@
         <v>6625322648</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D36" s="10">
         <v>2</v>
@@ -4676,7 +4640,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G36" s="10">
         <v>7</v>
@@ -4690,7 +4654,7 @@
         <v>6625745652</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="D37" s="18">
         <v>4</v>
@@ -4699,7 +4663,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G37" s="18">
         <v>7</v>
@@ -4713,7 +4677,7 @@
         <v>6625321638</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
@@ -4722,7 +4686,7 @@
         <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G38" s="4">
         <v>7</v>
@@ -4736,7 +4700,7 @@
         <v>6625244629</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="D39" s="12">
         <v>4</v>
@@ -4745,7 +4709,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G39" s="12">
         <v>8</v>
@@ -4759,7 +4723,7 @@
         <v>6625765661</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D40" s="14">
         <v>6</v>
@@ -4768,7 +4732,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="G40" s="14">
         <v>8</v>
@@ -4792,13 +4756,13 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4806,16 +4770,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
         <v>160</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>162</v>
-      </c>
-      <c r="E2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4823,16 +4787,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" t="s">
         <v>164</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>166</v>
-      </c>
-      <c r="E3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4840,16 +4804,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" t="s">
         <v>168</v>
       </c>
-      <c r="C4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
-      </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4857,16 +4821,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
         <v>170</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>171</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>172</v>
-      </c>
-      <c r="E5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4874,16 +4838,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4891,16 +4855,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" t="s">
         <v>176</v>
       </c>
-      <c r="C7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" t="s">
-        <v>177</v>
-      </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4908,16 +4872,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" t="s">
         <v>178</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>179</v>
       </c>
-      <c r="D8" t="s">
-        <v>180</v>
-      </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4925,16 +4889,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" t="s">
         <v>181</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>182</v>
       </c>
-      <c r="D9" t="s">
-        <v>183</v>
-      </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4942,16 +4906,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" t="s">
         <v>184</v>
       </c>
-      <c r="C10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" t="s">
-        <v>185</v>
-      </c>
       <c r="E10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4959,16 +4923,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" t="s">
         <v>186</v>
       </c>
-      <c r="C11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" t="s">
-        <v>187</v>
-      </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4976,16 +4940,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" t="s">
         <v>188</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>189</v>
       </c>
-      <c r="D12" t="s">
-        <v>190</v>
-      </c>
       <c r="E12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4993,16 +4957,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" t="s">
         <v>191</v>
       </c>
-      <c r="C13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" t="s">
-        <v>192</v>
-      </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -5027,22 +4991,22 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" t="s">
         <v>194</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>195</v>
-      </c>
-      <c r="H1" t="s">
-        <v>196</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -5056,22 +5020,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="D2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="G2" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -5079,22 +5043,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="C3" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G3" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -5102,19 +5066,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C4" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="D4" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -5122,19 +5086,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C5" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="D5" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5142,22 +5106,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="D6" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G6" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -5165,22 +5129,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G7" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -5188,22 +5152,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C8" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D8" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" t="s">
         <v>490</v>
-      </c>
-      <c r="G8" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -5211,22 +5175,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C9" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D9" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="G9" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -5234,22 +5198,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C10" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D10" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="G10" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -5257,22 +5221,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="D11" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G11" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -5280,22 +5244,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D12" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G12" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -5303,22 +5267,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C13" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="D13" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G13" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -5326,22 +5290,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D14" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G14" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -5349,22 +5313,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="D15" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G15" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5372,22 +5336,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C16" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="D16" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G16" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -5395,22 +5359,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="C17" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G17" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -5418,22 +5382,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C18" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="D18" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G18" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -5441,22 +5405,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C19" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D19" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G19" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -5464,22 +5428,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C20" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D20" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G20" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -5487,22 +5451,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C21" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="D21" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" t="s">
+        <v>482</v>
+      </c>
+      <c r="G21" t="s">
         <v>494</v>
-      </c>
-      <c r="G21" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -5510,22 +5474,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C22" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="D22" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="G22" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -5533,19 +5497,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C23" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D23" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -5553,19 +5517,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C24" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="D24" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -5573,10 +5537,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C25" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D25">
         <v>2024</v>
@@ -5585,7 +5549,7 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -5593,10 +5557,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -5605,7 +5569,7 @@
         <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -5613,10 +5577,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C27" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D27">
         <v>2025</v>
@@ -5625,10 +5589,10 @@
         <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G27" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -5636,10 +5600,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C28" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D28">
         <v>2024</v>
@@ -5648,10 +5612,10 @@
         <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G28" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -5659,10 +5623,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C29" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D29">
         <v>2023</v>
@@ -5671,10 +5635,10 @@
         <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="G29" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -5682,10 +5646,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C30" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="D30">
         <v>2026</v>
@@ -5694,10 +5658,10 @@
         <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="G30" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -5705,10 +5669,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C31" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D31">
         <v>2026</v>
@@ -5717,10 +5681,10 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="G31" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -5728,10 +5692,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C32" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="D32">
         <v>2025</v>
@@ -5740,10 +5704,10 @@
         <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G32" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -5751,10 +5715,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C33" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D33">
         <v>2024</v>
@@ -5763,10 +5727,10 @@
         <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="G33" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -5774,10 +5738,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C34" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="D34">
         <v>2024</v>
@@ -5786,10 +5750,10 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="G34" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="145" x14ac:dyDescent="0.35">
@@ -5797,10 +5761,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C35" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D35">
         <v>2024</v>
@@ -5809,10 +5773,10 @@
         <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -5820,10 +5784,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C36" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="D36">
         <v>2023</v>
@@ -5832,403 +5796,100 @@
         <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G36" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C37" t="s">
-        <v>536</v>
-      </c>
-      <c r="D37" t="s">
-        <v>481</v>
-      </c>
-      <c r="E37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" t="s">
-        <v>552</v>
-      </c>
-      <c r="G37" t="s">
-        <v>562</v>
-      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C38" t="s">
-        <v>537</v>
-      </c>
-      <c r="D38" t="s">
-        <v>483</v>
-      </c>
-      <c r="E38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" t="s">
-        <v>553</v>
-      </c>
-      <c r="G38" t="s">
-        <v>563</v>
-      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C39" t="s">
-        <v>538</v>
-      </c>
-      <c r="D39" t="s">
-        <v>485</v>
-      </c>
-      <c r="E39" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" t="s">
-        <v>552</v>
-      </c>
-      <c r="G39" t="s">
-        <v>564</v>
-      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C40" t="s">
-        <v>539</v>
-      </c>
-      <c r="D40" t="s">
-        <v>481</v>
-      </c>
-      <c r="E40" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" t="s">
-        <v>487</v>
-      </c>
-      <c r="G40" t="s">
-        <v>565</v>
-      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C41" t="s">
-        <v>540</v>
-      </c>
-      <c r="D41" t="s">
-        <v>483</v>
-      </c>
-      <c r="E41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" t="s">
-        <v>552</v>
-      </c>
-      <c r="G41" t="s">
-        <v>566</v>
-      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C42" t="s">
-        <v>541</v>
-      </c>
-      <c r="D42" t="s">
-        <v>483</v>
-      </c>
-      <c r="E42" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42" t="s">
-        <v>554</v>
-      </c>
-      <c r="G42" t="s">
-        <v>567</v>
-      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C43" t="s">
-        <v>542</v>
-      </c>
-      <c r="D43" t="s">
-        <v>483</v>
-      </c>
-      <c r="E43" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" t="s">
-        <v>554</v>
-      </c>
-      <c r="G43" t="s">
-        <v>510</v>
-      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C44" t="s">
-        <v>541</v>
-      </c>
-      <c r="D44" t="s">
-        <v>485</v>
-      </c>
-      <c r="E44" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" t="s">
-        <v>555</v>
-      </c>
-      <c r="G44" t="s">
-        <v>567</v>
-      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C45" t="s">
-        <v>543</v>
-      </c>
-      <c r="D45" t="s">
-        <v>481</v>
-      </c>
-      <c r="E45" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" t="s">
-        <v>556</v>
-      </c>
-      <c r="G45" t="s">
-        <v>568</v>
-      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C46" t="s">
-        <v>544</v>
-      </c>
-      <c r="D46" t="s">
-        <v>482</v>
-      </c>
-      <c r="E46" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" t="s">
-        <v>557</v>
-      </c>
-      <c r="G46" t="s">
-        <v>566</v>
-      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C47" t="s">
-        <v>545</v>
-      </c>
-      <c r="D47" t="s">
-        <v>483</v>
-      </c>
-      <c r="E47" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" t="s">
-        <v>558</v>
-      </c>
-      <c r="G47" t="s">
-        <v>564</v>
-      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C48" t="s">
-        <v>546</v>
-      </c>
-      <c r="D48" t="s">
-        <v>481</v>
-      </c>
-      <c r="E48" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C49" t="s">
-        <v>547</v>
-      </c>
-      <c r="D49" t="s">
-        <v>482</v>
-      </c>
-      <c r="E49" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C50" t="s">
-        <v>548</v>
-      </c>
-      <c r="D50" t="s">
-        <v>482</v>
-      </c>
-      <c r="E50" t="s">
-        <v>40</v>
-      </c>
-      <c r="F50" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C51" t="s">
-        <v>549</v>
-      </c>
-      <c r="D51" t="s">
-        <v>483</v>
-      </c>
-      <c r="E51" t="s">
-        <v>40</v>
-      </c>
-      <c r="F51" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C52" t="s">
-        <v>549</v>
-      </c>
-      <c r="D52" t="s">
-        <v>483</v>
-      </c>
-      <c r="E52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F52" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="C53" t="s">
-        <v>550</v>
-      </c>
-      <c r="D53" t="s">
-        <v>483</v>
-      </c>
-      <c r="E53" t="s">
-        <v>40</v>
-      </c>
-      <c r="F53" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C54" t="s">
-        <v>551</v>
-      </c>
-      <c r="D54" t="s">
-        <v>483</v>
-      </c>
-      <c r="E54" t="s">
-        <v>40</v>
-      </c>
-      <c r="F54" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -6252,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -6264,7 +5925,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -6272,22 +5933,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" t="s">
         <v>203</v>
-      </c>
-      <c r="C2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -6295,19 +5956,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -6315,19 +5976,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -6335,16 +5996,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -6352,19 +6013,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -6374,8 +6035,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="19.7265625" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -6385,22 +6050,22 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" t="s">
         <v>194</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>195</v>
-      </c>
-      <c r="H1" t="s">
-        <v>196</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -6413,87 +6078,411 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>226</v>
+      <c r="B2" s="2" t="s">
+        <v>506</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>524</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>469</v>
       </c>
       <c r="E2" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>228</v>
+        <v>540</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>550</v>
       </c>
       <c r="H2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>232</v>
+      <c r="B3" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>525</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>471</v>
       </c>
       <c r="E3" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>233</v>
+        <v>541</v>
       </c>
       <c r="G3" t="s">
-        <v>198</v>
+        <v>551</v>
       </c>
       <c r="H3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>235</v>
+      <c r="B4" s="2" t="s">
+        <v>508</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>526</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>473</v>
       </c>
       <c r="E4" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>236</v>
+        <v>540</v>
       </c>
       <c r="G4" t="s">
-        <v>199</v>
+        <v>552</v>
       </c>
       <c r="H4" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="I4" t="s">
-        <v>238</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D5" t="s">
+        <v>469</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D6" t="s">
+        <v>471</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>540</v>
+      </c>
+      <c r="G6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D7" t="s">
+        <v>471</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>542</v>
+      </c>
+      <c r="G7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C8" t="s">
+        <v>530</v>
+      </c>
+      <c r="D8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>542</v>
+      </c>
+      <c r="G8" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" t="s">
+        <v>529</v>
+      </c>
+      <c r="D9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>543</v>
+      </c>
+      <c r="G9" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C10" t="s">
+        <v>531</v>
+      </c>
+      <c r="D10" t="s">
+        <v>469</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>544</v>
+      </c>
+      <c r="G10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C11" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" t="s">
+        <v>470</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>545</v>
+      </c>
+      <c r="G11" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C12" t="s">
+        <v>533</v>
+      </c>
+      <c r="D12" t="s">
+        <v>471</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>546</v>
+      </c>
+      <c r="G12" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C13" t="s">
+        <v>534</v>
+      </c>
+      <c r="D13" t="s">
+        <v>469</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C14" t="s">
+        <v>535</v>
+      </c>
+      <c r="D14" t="s">
+        <v>470</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C15" t="s">
+        <v>536</v>
+      </c>
+      <c r="D15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D16" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C17" t="s">
+        <v>537</v>
+      </c>
+      <c r="D17" t="s">
+        <v>471</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C18" t="s">
+        <v>538</v>
+      </c>
+      <c r="D18" t="s">
+        <v>471</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C19" t="s">
+        <v>539</v>
+      </c>
+      <c r="D19" t="s">
+        <v>471</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
+++ b/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYDATA\Project\webte\te-upgris\src\data\dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1FD21A-0C9E-4EE7-AA44-96CC1C10532B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776EFE4-4E2F-412A-ACB3-3803125941D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="beranda" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="600">
   <si>
     <t>videoUrl</t>
   </si>
@@ -511,103 +511,25 @@
     <t>tingkat</t>
   </si>
   <si>
-    <t>PT PLN (Persero)</t>
-  </si>
-  <si>
     <t>BUMN</t>
   </si>
   <si>
-    <t>Program Magang &amp; Rekrutmen Lulusan</t>
-  </si>
-  <si>
     <t>Nasional</t>
   </si>
   <si>
-    <t>Siemens Indonesia</t>
-  </si>
-  <si>
     <t>Industri</t>
   </si>
   <si>
-    <t>Workshop IoT &amp; Industri 4.0</t>
-  </si>
-  <si>
     <t>Internasional</t>
   </si>
   <si>
-    <t>PT Schneider Electric Indonesia</t>
-  </si>
-  <si>
-    <t>Penyediaan Perangkat Lab &amp; Pelatihan</t>
-  </si>
-  <si>
-    <t>PDAM Tirta Moedal Semarang</t>
-  </si>
-  <si>
     <t>BUMD</t>
   </si>
   <si>
-    <t>Penelitian Efisiensi Pompa Listrik</t>
-  </si>
-  <si>
-    <t>Lokal</t>
-  </si>
-  <si>
-    <t>Universiti Teknologi Malaysia (UTM)</t>
-  </si>
-  <si>
-    <t>Joint Research &amp; Student Exchange</t>
-  </si>
-  <si>
-    <t>PT Pertamina EP</t>
-  </si>
-  <si>
-    <t>Penelitian Instrumentasi Kilang</t>
-  </si>
-  <si>
-    <t>BRIN (Badan Riset Inovasi Nasional)</t>
-  </si>
-  <si>
     <t>Pemerintah</t>
   </si>
   <si>
-    <t>Kolaborasi Riset Energi Terbarukan</t>
-  </si>
-  <si>
-    <t>SMK Negeri 4 Semarang</t>
-  </si>
-  <si>
-    <t>Pendidikan</t>
-  </si>
-  <si>
-    <t>Program Guru Tamu &amp; Magang Dosen</t>
-  </si>
-  <si>
-    <t>PT ABB Indonesia</t>
-  </si>
-  <si>
-    <t>Sertifikasi &amp; Pelatihan Teknik Kontrol</t>
-  </si>
-  <si>
-    <t>Pemkot Semarang - Dinas ESDM</t>
-  </si>
-  <si>
-    <t>Pendampingan Audit Energi Kota</t>
-  </si>
-  <si>
-    <t>IEEE Indonesia Section</t>
-  </si>
-  <si>
     <t>Asosiasi Profesi</t>
-  </si>
-  <si>
-    <t>Anggota &amp; Penyelenggara Konferensi</t>
-  </si>
-  <si>
-    <t>Asosiasi Profesi Insinyur Indonesia (PII)</t>
-  </si>
-  <si>
-    <t>Sertifikasi Kompetensi Dosen &amp; Lulusan</t>
   </si>
   <si>
     <t>dosen</t>
@@ -1834,6 +1756,102 @@
   </si>
   <si>
     <t>Kuliah Kerja Nyata (KKN)</t>
+  </si>
+  <si>
+    <t>CV Standar</t>
+  </si>
+  <si>
+    <t>PT Autonics Indonesia</t>
+  </si>
+  <si>
+    <t>PT. AUTENTIK KARYA ANALITIKA</t>
+  </si>
+  <si>
+    <t>PT Norgantara</t>
+  </si>
+  <si>
+    <t>Guangxi Modern Polytechnic College</t>
+  </si>
+  <si>
+    <t>PT Mitra Daya Teknika</t>
+  </si>
+  <si>
+    <t>SMU Setia Budi</t>
+  </si>
+  <si>
+    <t>Universiti Teknologi Malaysia</t>
+  </si>
+  <si>
+    <t>Neijiang Vocational and Technical College China</t>
+  </si>
+  <si>
+    <t>PT. FHG</t>
+  </si>
+  <si>
+    <t>Universitas Muhammadiyah Semarang</t>
+  </si>
+  <si>
+    <t>Universitas Teknologi Yogyakarta</t>
+  </si>
+  <si>
+    <t>LSK GEMA PEDEKABE</t>
+  </si>
+  <si>
+    <t>Laksana Bus</t>
+  </si>
+  <si>
+    <t>Iloilo Science and Technology University</t>
+  </si>
+  <si>
+    <t>CV. Bintang Anugerah Elektrik</t>
+  </si>
+  <si>
+    <t>PT. Omni Electrindo</t>
+  </si>
+  <si>
+    <t>NUEVA ECIJA UNIVERSITY OF SCIENCE AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>XXVTC ( Xinxiang Vocational and Technical College)</t>
+  </si>
+  <si>
+    <t>PT Nocola IoT Solution</t>
+  </si>
+  <si>
+    <t>PT. Asia Pacific Fibers Tbk.</t>
+  </si>
+  <si>
+    <t>Magang Industri</t>
+  </si>
+  <si>
+    <t>Pelatihan dan Pengabdian</t>
+  </si>
+  <si>
+    <t>Colaborative Teaching</t>
+  </si>
+  <si>
+    <t>Kerjasama Pendidikan</t>
+  </si>
+  <si>
+    <t>Gues Lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kunjungan Benchmark </t>
+  </si>
+  <si>
+    <t>Student Exchange</t>
+  </si>
+  <si>
+    <t>Pertukaran dosen dan mahasiswa</t>
+  </si>
+  <si>
+    <t>Mitra DUDI Penyusunan Kurikulum</t>
+  </si>
+  <si>
+    <t>Wilayah</t>
+  </si>
+  <si>
+    <t>Lembaga Sertifikasi</t>
   </si>
 </sst>
 </file>
@@ -2344,81 +2362,81 @@
         <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="D1" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="F1" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="G1" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="H1" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="I1" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="J1" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="K1" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="L1" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="M1" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="N1" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="O1" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="P1" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="Q1" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="R1" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="S1" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="G2" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="H2">
         <v>203</v>
@@ -2427,34 +2445,34 @@
         <v>3.32</v>
       </c>
       <c r="J2" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="K2" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="L2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="M2" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="N2" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="O2" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="Q2" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="R2" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="S2" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2475,7 +2493,7 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
         <v>157</v>
@@ -2484,10 +2502,10 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="G1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -2495,22 +2513,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="G2" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2518,22 +2536,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="G3" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -2541,22 +2559,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F4" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="G4" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -2564,22 +2582,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="G5" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -2587,22 +2605,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F6" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="G6" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2620,31 +2638,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="C1" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="D1" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="E1" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="F1" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="I1" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="J1" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2652,31 +2670,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="F2" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="G2" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="I2" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2684,31 +2702,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="D3" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="E3" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="F3" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="G3" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="H3" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="I3" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="J3" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2716,31 +2734,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="C4" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="D4" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E4" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="G4" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="H4" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="I4" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="J4" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2748,31 +2766,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="E5" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="F5" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="G5" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="H5" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="I5" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="J5" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2793,7 +2811,7 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2802,7 +2820,7 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2810,19 +2828,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="D2" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F2" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2830,19 +2848,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2850,19 +2868,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="D4" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2870,19 +2888,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2890,19 +2908,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="D6" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F6" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2910,19 +2928,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="D7" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F7" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2930,19 +2948,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D8" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F8" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2950,19 +2968,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="C9" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="D9" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F9" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2970,19 +2988,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="C10" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F10" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2990,19 +3008,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="C11" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F11" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -3545,10 +3563,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="D2" t="s">
         <v>126</v>
@@ -3557,10 +3575,10 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="G2" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="H2" t="s">
         <v>122</v>
@@ -3580,10 +3598,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
         <v>126</v>
@@ -3592,13 +3610,13 @@
         <v>127</v>
       </c>
       <c r="F3" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="G3" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="H3" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="I3" t="s">
         <v>128</v>
@@ -3615,10 +3633,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="C4" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
         <v>126</v>
@@ -3627,10 +3645,10 @@
         <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="H4" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I4" t="s">
         <v>131</v>
@@ -3647,10 +3665,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
         <v>126</v>
@@ -3659,13 +3677,13 @@
         <v>133</v>
       </c>
       <c r="F5" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="G5" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="H5" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I5" t="s">
         <v>134</v>
@@ -3682,10 +3700,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="C6" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="D6" t="s">
         <v>136</v>
@@ -3694,10 +3712,10 @@
         <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="G6" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="H6" t="s">
         <v>138</v>
@@ -3717,10 +3735,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="D7" t="s">
         <v>136</v>
@@ -3729,10 +3747,10 @@
         <v>141</v>
       </c>
       <c r="F7" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="G7" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
@@ -3749,10 +3767,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C8" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="D8" t="s">
         <v>126</v>
@@ -3761,7 +3779,7 @@
         <v>144</v>
       </c>
       <c r="G8" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="H8" t="s">
         <v>138</v>
@@ -3781,10 +3799,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="C9" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3793,10 +3811,10 @@
         <v>147</v>
       </c>
       <c r="F9" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="G9" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="I9" t="s">
         <v>148</v>
@@ -3849,7 +3867,7 @@
         <v>6625332615</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="D2" s="4">
         <v>3</v>
@@ -3858,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -3872,7 +3890,7 @@
         <v>6625331620</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="D3" s="6">
         <v>3</v>
@@ -3881,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G3" s="6">
         <v>1</v>
@@ -3895,7 +3913,7 @@
         <v>6625332616</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
@@ -3904,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -3918,7 +3936,7 @@
         <v>6625331635</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -3927,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G5" s="8">
         <v>3</v>
@@ -3941,7 +3959,7 @@
         <v>6625331617</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="D6" s="10">
         <v>3</v>
@@ -3950,7 +3968,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G6" s="10">
         <v>3</v>
@@ -3964,7 +3982,7 @@
         <v>6625332650</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
@@ -3973,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -3987,7 +4005,7 @@
         <v>6625431653</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="D8" s="6">
         <v>3</v>
@@ -3996,7 +4014,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G8" s="6">
         <v>3</v>
@@ -4019,7 +4037,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G9" s="12">
         <v>4</v>
@@ -4033,7 +4051,7 @@
         <v>6625331618</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="D10" s="14">
         <v>3</v>
@@ -4042,7 +4060,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G10" s="14">
         <v>4</v>
@@ -4056,7 +4074,7 @@
         <v>6625232625</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="D11" s="8">
         <v>3</v>
@@ -4065,7 +4083,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G11" s="8">
         <v>4</v>
@@ -4079,7 +4097,7 @@
         <v>6625331634</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="D12" s="16">
         <v>3</v>
@@ -4088,7 +4106,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G12" s="16">
         <v>4</v>
@@ -4102,7 +4120,7 @@
         <v>6625131657</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="D13" s="10">
         <v>3</v>
@@ -4111,7 +4129,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G13" s="10">
         <v>4</v>
@@ -4125,7 +4143,7 @@
         <v>6625131660</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="D14" s="18">
         <v>3</v>
@@ -4134,7 +4152,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G14" s="18">
         <v>4</v>
@@ -4148,7 +4166,7 @@
         <v>6625331636</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
@@ -4157,7 +4175,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G15" s="4">
         <v>4</v>
@@ -4171,7 +4189,7 @@
         <v>6625332606</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="D16" s="12">
         <v>3</v>
@@ -4180,7 +4198,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G16" s="12">
         <v>5</v>
@@ -4194,7 +4212,7 @@
         <v>6625221622</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
@@ -4203,7 +4221,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="G17" s="14">
         <v>5</v>
@@ -4217,7 +4235,7 @@
         <v>6625322626</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="D18" s="8">
         <v>2</v>
@@ -4226,7 +4244,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G18" s="8">
         <v>5</v>
@@ -4240,7 +4258,7 @@
         <v>6625324628</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="D19" s="16">
         <v>2</v>
@@ -4249,7 +4267,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G19" s="16">
         <v>5</v>
@@ -4263,7 +4281,7 @@
         <v>6625332630</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="D20" s="10">
         <v>3</v>
@@ -4272,7 +4290,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G20" s="10">
         <v>5</v>
@@ -4286,7 +4304,7 @@
         <v>6625331649</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="D21" s="18">
         <v>3</v>
@@ -4295,7 +4313,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G21" s="18">
         <v>5</v>
@@ -4309,7 +4327,7 @@
         <v>6625331656</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -4318,7 +4336,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G22" s="4">
         <v>5</v>
@@ -4332,7 +4350,7 @@
         <v>6625221605</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
@@ -4341,7 +4359,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="G23" s="6">
         <v>6</v>
@@ -4355,7 +4373,7 @@
         <v>6625332612</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
       <c r="D24" s="12">
         <v>3</v>
@@ -4364,7 +4382,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G24" s="12">
         <v>6</v>
@@ -4378,7 +4396,7 @@
         <v>6625321614</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -4387,7 +4405,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
@@ -4401,7 +4419,7 @@
         <v>6625332623</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="D26" s="8">
         <v>3</v>
@@ -4410,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G26" s="8">
         <v>6</v>
@@ -4424,7 +4442,7 @@
         <v>6625241624</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="D27" s="16">
         <v>4</v>
@@ -4433,7 +4451,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G27" s="16">
         <v>6</v>
@@ -4447,7 +4465,7 @@
         <v>6625321633</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="D28" s="10">
         <v>2</v>
@@ -4456,7 +4474,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G28" s="10">
         <v>6</v>
@@ -4470,7 +4488,7 @@
         <v>6625321647</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>586</v>
+        <v>560</v>
       </c>
       <c r="D29" s="18">
         <v>2</v>
@@ -4479,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="G29" s="18">
         <v>6</v>
@@ -4493,7 +4511,7 @@
         <v>6625332651</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="D30" s="4">
         <v>3</v>
@@ -4502,7 +4520,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G30" s="4">
         <v>6</v>
@@ -4516,7 +4534,7 @@
         <v>6625322603</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="D31" s="6">
         <v>3</v>
@@ -4525,7 +4543,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G31" s="6">
         <v>7</v>
@@ -4548,7 +4566,7 @@
         <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G32" s="12">
         <v>7</v>
@@ -4562,7 +4580,7 @@
         <v>6625422627</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -4571,7 +4589,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G33" s="14">
         <v>7</v>
@@ -4585,7 +4603,7 @@
         <v>6625421631</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="D34" s="8">
         <v>2</v>
@@ -4594,7 +4612,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G34" s="8">
         <v>7</v>
@@ -4608,7 +4626,7 @@
         <v>6625421632</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>590</v>
+        <v>564</v>
       </c>
       <c r="D35" s="16">
         <v>2</v>
@@ -4617,7 +4635,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G35" s="16">
         <v>7</v>
@@ -4631,7 +4649,7 @@
         <v>6625322648</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D36" s="10">
         <v>2</v>
@@ -4640,7 +4658,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G36" s="10">
         <v>7</v>
@@ -4654,7 +4672,7 @@
         <v>6625745652</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="D37" s="18">
         <v>4</v>
@@ -4663,7 +4681,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G37" s="18">
         <v>7</v>
@@ -4677,7 +4695,7 @@
         <v>6625321638</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
@@ -4686,7 +4704,7 @@
         <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="G38" s="4">
         <v>7</v>
@@ -4700,7 +4718,7 @@
         <v>6625244629</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="D39" s="12">
         <v>4</v>
@@ -4709,7 +4727,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="G39" s="12">
         <v>8</v>
@@ -4723,7 +4741,7 @@
         <v>6625765661</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="D40" s="14">
         <v>6</v>
@@ -4732,7 +4750,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G40" s="14">
         <v>8</v>
@@ -4745,8 +4763,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="48.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -4770,16 +4792,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C2" t="s">
         <v>159</v>
       </c>
-      <c r="C2" t="s">
-        <v>160</v>
-      </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>589</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4787,16 +4809,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>569</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>590</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4804,16 +4826,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>570</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>589</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4821,16 +4843,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>571</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>590</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4838,16 +4860,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>572</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>591</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4855,16 +4877,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>573</v>
       </c>
       <c r="C7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" t="s">
+        <v>589</v>
+      </c>
+      <c r="E7" t="s">
         <v>160</v>
-      </c>
-      <c r="D7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4872,16 +4894,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>574</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>179</v>
+        <v>592</v>
       </c>
       <c r="E8" t="s">
-        <v>162</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4889,16 +4911,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>575</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>593</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4906,16 +4928,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>576</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>593</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4923,16 +4945,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>577</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>589</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4940,16 +4962,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>578</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>591</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4957,16 +4979,186 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>579</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s">
-        <v>191</v>
+        <v>594</v>
       </c>
       <c r="E13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>580</v>
+      </c>
+      <c r="C14" t="s">
+        <v>599</v>
+      </c>
+      <c r="D14" t="s">
+        <v>591</v>
+      </c>
+      <c r="E14" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>581</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" t="s">
+        <v>589</v>
+      </c>
+      <c r="E15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>582</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>595</v>
+      </c>
+      <c r="E16" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>583</v>
+      </c>
+      <c r="C17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" t="s">
+        <v>589</v>
+      </c>
+      <c r="E17" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>584</v>
+      </c>
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" t="s">
+        <v>589</v>
+      </c>
+      <c r="E18" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>585</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>596</v>
+      </c>
+      <c r="E19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>586</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>570</v>
+      </c>
+      <c r="C21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" t="s">
+        <v>589</v>
+      </c>
+      <c r="E21" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>587</v>
+      </c>
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" t="s">
+        <v>597</v>
+      </c>
+      <c r="E22" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>588</v>
+      </c>
+      <c r="C23" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" t="s">
+        <v>597</v>
+      </c>
+      <c r="E23" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -4991,7 +5183,7 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
@@ -5000,13 +5192,13 @@
         <v>157</v>
       </c>
       <c r="F1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="H1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -5020,22 +5212,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="G2" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -5043,22 +5235,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="C3" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="G3" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -5066,19 +5258,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="C4" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="D4" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -5086,19 +5278,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="C5" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="D5" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5106,22 +5298,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="D6" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="G6" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -5129,22 +5321,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="C7" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="D7" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="G7" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -5152,22 +5344,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="C8" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="D8" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="G8" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -5175,22 +5367,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D9" t="s">
         <v>444</v>
-      </c>
-      <c r="D9" t="s">
-        <v>470</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="G9" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -5198,22 +5390,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="C10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D10" t="s">
         <v>445</v>
-      </c>
-      <c r="D10" t="s">
-        <v>471</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="G10" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -5221,22 +5413,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="D11" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="G11" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -5244,22 +5436,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="C12" t="s">
+        <v>421</v>
+      </c>
+      <c r="D12" t="s">
         <v>447</v>
-      </c>
-      <c r="D12" t="s">
-        <v>473</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G12" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -5267,22 +5459,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G13" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -5290,22 +5482,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="C14" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="D14" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G14" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -5313,22 +5505,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="C15" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G15" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5336,22 +5528,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="C16" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="D16" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G16" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -5359,22 +5551,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="C17" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -5382,22 +5574,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="D18" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G18" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -5405,22 +5597,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="C19" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="D19" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G19" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -5428,22 +5620,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="C20" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="D20" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G20" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -5451,22 +5643,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="C21" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D21" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G21" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -5474,22 +5666,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="D22" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G22" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -5497,19 +5689,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="C23" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="D23" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -5517,19 +5709,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="C24" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="D24" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -5537,10 +5729,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="C25" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="D25">
         <v>2024</v>
@@ -5549,7 +5741,7 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -5557,10 +5749,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="C26" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -5569,7 +5761,7 @@
         <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -5577,10 +5769,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="D27">
         <v>2025</v>
@@ -5589,10 +5781,10 @@
         <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="G27" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -5600,10 +5792,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="C28" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="D28">
         <v>2024</v>
@@ -5612,10 +5804,10 @@
         <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="G28" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -5623,10 +5815,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="C29" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="D29">
         <v>2023</v>
@@ -5635,10 +5827,10 @@
         <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="G29" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -5646,10 +5838,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="C30" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="D30">
         <v>2026</v>
@@ -5658,10 +5850,10 @@
         <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="G30" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -5669,10 +5861,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="C31" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="D31">
         <v>2026</v>
@@ -5681,10 +5873,10 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="G31" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -5692,10 +5884,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="C32" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="D32">
         <v>2025</v>
@@ -5704,10 +5896,10 @@
         <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="G32" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -5715,10 +5907,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="D33">
         <v>2024</v>
@@ -5727,10 +5919,10 @@
         <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="G33" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -5738,10 +5930,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C34" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="D34">
         <v>2024</v>
@@ -5750,10 +5942,10 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="G34" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="145" x14ac:dyDescent="0.35">
@@ -5761,10 +5953,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="C35" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="D35">
         <v>2024</v>
@@ -5773,10 +5965,10 @@
         <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -5784,10 +5976,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="C36" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="D36">
         <v>2023</v>
@@ -5796,10 +5988,10 @@
         <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="G36" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -5913,7 +6105,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -5925,7 +6117,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -5933,22 +6125,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H2" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -5956,19 +6148,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -5976,19 +6168,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="G4" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -5996,16 +6188,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="D5" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -6013,19 +6205,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -6050,7 +6242,7 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
         <v>51</v>
@@ -6059,13 +6251,13 @@
         <v>157</v>
       </c>
       <c r="F1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="H1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
@@ -6079,31 +6271,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="D2" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
         <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="G2" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="I2" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="J2" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -6111,25 +6303,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="C3" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>541</v>
+        <v>515</v>
       </c>
       <c r="G3" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="H3" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -6137,28 +6329,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="C4" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="D4" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="G4" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="H4" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="I4" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -6166,22 +6358,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="D5" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
         <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="G5" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -6189,22 +6381,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="C6" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="D6" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="G6" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -6212,22 +6404,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="C7" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="D7" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="G7" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -6235,22 +6427,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="C8" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="D8" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="G8" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -6258,22 +6450,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="C9" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="D9" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>543</v>
+        <v>517</v>
       </c>
       <c r="G9" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -6281,22 +6473,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="C10" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="D10" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
       <c r="G10" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -6304,22 +6496,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="C11" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="D11" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="G11" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -6327,22 +6519,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="C12" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="D12" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="G12" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -6350,19 +6542,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="C13" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -6370,19 +6562,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="C14" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -6390,19 +6582,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="C15" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -6410,19 +6602,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="C16" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="D16" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -6430,19 +6622,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="C17" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="D17" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -6450,19 +6642,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="C18" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="D18" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -6470,19 +6662,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="C19" t="s">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="D19" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
+++ b/te-upgris/src/data/dummy/Hasil_Konversi_JSON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYDATA\Project\webte\te-upgris\src\data\dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776EFE4-4E2F-412A-ACB3-3803125941D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECE2422-B83D-4EB4-9B4D-BF02186550F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="beranda" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="655">
   <si>
     <t>videoUrl</t>
   </si>
@@ -748,82 +748,22 @@
     <t>keterangan</t>
   </si>
   <si>
-    <t>Smart Grid Optimization Using Particle Swarm Algorithm</t>
-  </si>
-  <si>
-    <t>Dr. Eng. Agus Setiawan</t>
-  </si>
-  <si>
     <t>Jurnal Internasional</t>
   </si>
   <si>
     <t>2025</t>
   </si>
   <si>
-    <t>https://ieeexplore.ieee.org/dummy1</t>
-  </si>
-  <si>
-    <t>IEEE Transactions on Power Systems, Q1</t>
-  </si>
-  <si>
-    <t>IoT-Based Power Quality Monitoring System</t>
-  </si>
-  <si>
-    <t>Ir. Budi Hartono</t>
-  </si>
-  <si>
     <t>Jurnal Nasional</t>
   </si>
   <si>
-    <t>https://journal.upgris.ac.id/dummy2</t>
-  </si>
-  <si>
-    <t>Jurnal Teknik Elektro Indonesia, Sinta 2</t>
-  </si>
-  <si>
-    <t>Deep Learning for Power System Fault Classification</t>
-  </si>
-  <si>
-    <t>Diah Permata Sari</t>
-  </si>
-  <si>
     <t>Prosiding Internasional</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>https://ieeexplore.ieee.org/dummy3</t>
-  </si>
-  <si>
-    <t>IEEE TENCON 2024</t>
-  </si>
-  <si>
-    <t>Robot Vision for High Voltage Line Inspection</t>
-  </si>
-  <si>
-    <t>Yoga Pratama</t>
-  </si>
-  <si>
     <t>Prosiding Nasional</t>
-  </si>
-  <si>
-    <t>https://senatik.upgris.ac.id/dummy4</t>
-  </si>
-  <si>
-    <t>SENATIK 2024</t>
-  </si>
-  <si>
-    <t>Renewable Energy Adoption in Rural Indonesia</t>
-  </si>
-  <si>
-    <t>Muhamad Fauzi</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/dummy5</t>
-  </si>
-  <si>
-    <t>Renewable &amp; Sustainable Energy Reviews, Q1</t>
   </si>
   <si>
     <t>tag</t>
@@ -1852,13 +1792,238 @@
   </si>
   <si>
     <t>Lembaga Sertifikasi</t>
+  </si>
+  <si>
+    <t>Design of Water Pump Station Control in Polder System using IoT and Hybrid Fuzzy Neural Network</t>
+  </si>
+  <si>
+    <t>A Comprehensive Analysis of Mask Detection Using Convolutional Neural Networks (CNN) and Single Shot Multibox Detector (SSD) Approach</t>
+  </si>
+  <si>
+    <t>Review Paper on Bluetooth Based Home Automation Using Android Phone</t>
+  </si>
+  <si>
+    <t>Feasibility Study of Solar Power Generation System for Public Street Lighting</t>
+  </si>
+  <si>
+    <t>The Potential of Mechanic Vibration for Generating Electric Energy</t>
+  </si>
+  <si>
+    <t>Power Regulation on PV and Grid with Monitoring Load Power in Residential</t>
+  </si>
+  <si>
+    <t>Multi-Inverter Coordinated Control on AC Microgrid for Increased Load Power</t>
+  </si>
+  <si>
+    <t>Real-Time Microgrid For Submersible Pump Energy Consumption Based On Fuzzy Logic Controller</t>
+  </si>
+  <si>
+    <t>Power management on DC microgrid with new DC coupling based on fuzzy logic</t>
+  </si>
+  <si>
+    <t>Solar power and multi-battery for new configuration DC microgrid using centralized control</t>
+  </si>
+  <si>
+    <t>Real-Time Microgrid Centralized Control For Consuming Water Pump</t>
+  </si>
+  <si>
+    <t>Coordinated Control of AC Microgrid for Increase Load Power Using Multi-Inverter</t>
+  </si>
+  <si>
+    <t>Enhancement DC Microgrid Power Stability with a Centralized</t>
+  </si>
+  <si>
+    <t>Improvement the Capacity of Electrical Energy in Residential Using PV with On-Grid System</t>
+  </si>
+  <si>
+    <t>Coordinated Control of Battery Energy Storage System Based on Fuzzy Logic for Microgrid with Modified AC Coupling Configuration</t>
+  </si>
+  <si>
+    <t>Effectiveness of implementing deep learning approach using PBL with PhET simulation on students’ interest and collaboration</t>
+  </si>
+  <si>
+    <t>Study on Local-Structure Symmetrization of K2XF6 Crystals Doped with Mn4+ Ions by First-Principles Calculations</t>
+  </si>
+  <si>
+    <t>PROJECT-BASED LEARNING VIA TRADITIONAL GAME IN PHYSICS LEARNING: ITS IMPACT ON CRITICAL THINKING, CREATIVE THINKING, AND COLLABORATIVE SKILLS</t>
+  </si>
+  <si>
+    <t>Comprehensive observations on pendulum oscillation using stereo vision</t>
+  </si>
+  <si>
+    <t>Development of laboratory devices for real-time measurement of object 3D position using stereo cameras</t>
+  </si>
+  <si>
+    <t>System and method for stereoscopic image acquisition</t>
+  </si>
+  <si>
+    <t>3D Velocity Measurement of Translational Motion using a Stereo Camera</t>
+  </si>
+  <si>
+    <t>Soft starter induction motor three phase with fuzzy logic controller inside delta</t>
+  </si>
+  <si>
+    <t>Thermoacoustic design using stem of goose down stack</t>
+  </si>
+  <si>
+    <t>Thickness optimization of a triple-layered microwave absorber combining magnetic and dielectric particles</t>
+  </si>
+  <si>
+    <t>Digital Physics Module for 21st Century Education on New and Renewable Energy Based on the Dilemma-STEAM Learning Model</t>
+  </si>
+  <si>
+    <t>The Effectiveness of the Dilemma-STEAM Learning Model Based on Motion Graphic Videos in the Subject of Parabolic Motion</t>
+  </si>
+  <si>
+    <t>Development of educational videos on work and energy topics to support schoology based e-learning</t>
+  </si>
+  <si>
+    <t>Revitalizing circular motion topic learning through android application based on transformative learning</t>
+  </si>
+  <si>
+    <t>Preparation and Thickness Optimization of Graphenic-Based Carbon Material as a Microwave Absorber</t>
+  </si>
+  <si>
+    <t>Thickness optimization of a double-layered microwave absorber combining magnetic and dielectric particles</t>
+  </si>
+  <si>
+    <t>Chemical exfoliation and microwave absorption of reduced graphene oxide synthesized from old coconut shells</t>
+  </si>
+  <si>
+    <t>EFFECT OF PRIME MOVER REGENERATOR RADIUS ON THE PERFORMANCE AND CHARACTERISTIC OF ACOUSTIC FIELD OF THERMOACOUSTIC REFRIGERATOR DRIVEN BY PRIME MOVER</t>
+  </si>
+  <si>
+    <t>CONSTRUCTION AND TESTING OF SMALL-SCALE THERMOACOUSTIC ELECTRICITY GENERATOR WITH DIFFERENT HEATING POWER</t>
+  </si>
+  <si>
+    <t>Numerical Study on the Effect of Stack Radii on the Low Onset Heating Temperature and Efficiency of 4-Stage Thermoacoustic Engine</t>
+  </si>
+  <si>
+    <t>The effect of regenerator's radii on low heating temperature of 4-stage thermoacoustic engine utilizing solar and waste heat</t>
+  </si>
+  <si>
+    <t>Study on the optimal stack diameter on the efficiency of thermoacoustic engine</t>
+  </si>
+  <si>
+    <t>Performance of Thermoacoustic Cooler Driven by Thermoacoustic Engine with Different Flow Channel Radii</t>
+  </si>
+  <si>
+    <t>Imadudin Harjanto</t>
+  </si>
+  <si>
+    <t>Adhi Kusmantoro</t>
+  </si>
+  <si>
+    <t>Sigit Ristanto</t>
+  </si>
+  <si>
+    <t>AFFANDI FAISAL KURNIAWAN </t>
+  </si>
+  <si>
+    <t>Irna Farikhah</t>
+  </si>
+  <si>
+    <t> Q3 as Conference Proceedin Iop Conference Series Earth and Environmental Science</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin 2023 International Conference on Sustainable Emerging Innovations in Engineering and Technology Icse</t>
+  </si>
+  <si>
+    <t> no-Q as Journal Advance Sustainable Science Engineering and Technology</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin International Conference on Electrical Engineering Computer Science and Informatics Eecsi</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin 2023 6th International Conference on Vocational Education and Electrical Engineering Integrating Sca</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin 2023 International Conference on Advanced Mechatronics Intelligent Manufacture and Industrial Automa</t>
+  </si>
+  <si>
+    <t> Q2 as Journal Indonesian Journal of Electrical Engineering and Computer Science</t>
+  </si>
+  <si>
+    <t> Q3 as Journal Archives of Electrical Engineering</t>
+  </si>
+  <si>
+    <t> Q4 as Conference Proceedin E3s Web of Conferences</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin Proceedings Ieit 2023 2023 International Conference on Electrical and Information Technology</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin 2022 5th International Conference on Vocational Education and Electrical Engineering the Future of E</t>
+  </si>
+  <si>
+    <t> Q3 as Conference Proceedin E3s Web of Conferences</t>
+  </si>
+  <si>
+    <t> Q2 as Journal International Journal of Intelligent Engineering and Systems</t>
+  </si>
+  <si>
+    <t> Q3 as Journal Physics Education</t>
+  </si>
+  <si>
+    <t> Q2 as Journal Materials</t>
+  </si>
+  <si>
+    <t> Q2 as Journal Jurnal Pendidikan IPA Indonesia</t>
+  </si>
+  <si>
+    <t> Q4 as Conference Proceedin Aip Conference Proceedings</t>
+  </si>
+  <si>
+    <t> Q2 as Journal International Journal on Advanced Science Engineering and Information Technology</t>
+  </si>
+  <si>
+    <t> no-Q as Journal International Journal of Applied Engineering Research</t>
+  </si>
+  <si>
+    <t> Q3 as Journal Asia Pacific Journal of Science and Technology</t>
+  </si>
+  <si>
+    <t> Q3 as Conference Proceedin Journal of Physics Conference Series</t>
+  </si>
+  <si>
+    <t> Q3 as Journal Trends in Sciences</t>
+  </si>
+  <si>
+    <t> Q1 as Journal Materials Research Express</t>
+  </si>
+  <si>
+    <t> Q4 as Conference Proceedin Journal of Physics Conference Series</t>
+  </si>
+  <si>
+    <t> Q3 as Journal Thermal Science</t>
+  </si>
+  <si>
+    <t> Q1 as Journal Arabian Journal for Science and Engineering</t>
+  </si>
+  <si>
+    <t> no-Q as Conference Proceedin Proceedings of the 4th IEEE Eurasia Conference on Iot Communication and Engineering 2022 Ecice 2022</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85191245710&amp;origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85179128928&amp;origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85179139513&amp;origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85199799296&amp;origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/record/display.uri?eid=2-s2.0-85149390068&amp;origin=resultslist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1878,6 +2043,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1936,7 +2109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1959,12 +2132,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2019,8 +2208,12 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7F319157-8EBA-4E27-BD6D-ECC898A6892D}"/>
   </cellStyles>
@@ -2482,10 +2675,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2508,122 +2704,600 @@
         <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D2" t="s">
         <v>238</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>239</v>
       </c>
-      <c r="D2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F2" t="s">
-        <v>242</v>
+      <c r="F2" s="20" t="s">
+        <v>650</v>
       </c>
       <c r="G2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>581</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>618</v>
       </c>
       <c r="D3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F3" t="s">
-        <v>247</v>
+        <v>240</v>
+      </c>
+      <c r="E3">
+        <v>2023</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>651</v>
       </c>
       <c r="G3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>249</v>
+        <v>582</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F4" t="s">
-        <v>253</v>
+        <v>241</v>
+      </c>
+      <c r="E4">
+        <v>2023</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>652</v>
       </c>
       <c r="G4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>583</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>618</v>
       </c>
       <c r="D5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" t="s">
-        <v>258</v>
+        <v>243</v>
+      </c>
+      <c r="E5">
+        <v>2021</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>653</v>
       </c>
       <c r="G5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>584</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F6" t="s">
-        <v>262</v>
+        <v>238</v>
+      </c>
+      <c r="E6">
+        <v>2021</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>654</v>
       </c>
       <c r="G6" t="s">
-        <v>263</v>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C7" t="s">
+        <v>619</v>
+      </c>
+      <c r="G7" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>586</v>
+      </c>
+      <c r="C8" t="s">
+        <v>619</v>
+      </c>
+      <c r="E8">
+        <v>2023</v>
+      </c>
+      <c r="G8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>587</v>
+      </c>
+      <c r="C9" t="s">
+        <v>619</v>
+      </c>
+      <c r="E9">
+        <v>2023</v>
+      </c>
+      <c r="G9" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C10" t="s">
+        <v>619</v>
+      </c>
+      <c r="E10">
+        <v>2024</v>
+      </c>
+      <c r="G10" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>589</v>
+      </c>
+      <c r="C11" t="s">
+        <v>619</v>
+      </c>
+      <c r="G11" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>590</v>
+      </c>
+      <c r="C12" t="s">
+        <v>619</v>
+      </c>
+      <c r="G12" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>591</v>
+      </c>
+      <c r="C13" t="s">
+        <v>619</v>
+      </c>
+      <c r="G13" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>592</v>
+      </c>
+      <c r="C14" t="s">
+        <v>619</v>
+      </c>
+      <c r="G14" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>593</v>
+      </c>
+      <c r="C15" t="s">
+        <v>619</v>
+      </c>
+      <c r="G15" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>594</v>
+      </c>
+      <c r="C16" t="s">
+        <v>619</v>
+      </c>
+      <c r="G16" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>595</v>
+      </c>
+      <c r="C17" t="s">
+        <v>620</v>
+      </c>
+      <c r="G17" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C18" t="s">
+        <v>620</v>
+      </c>
+      <c r="G18" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>597</v>
+      </c>
+      <c r="C19" t="s">
+        <v>620</v>
+      </c>
+      <c r="G19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>598</v>
+      </c>
+      <c r="C20" t="s">
+        <v>620</v>
+      </c>
+      <c r="G20" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>599</v>
+      </c>
+      <c r="C21" t="s">
+        <v>620</v>
+      </c>
+      <c r="G21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>600</v>
+      </c>
+      <c r="C22" t="s">
+        <v>620</v>
+      </c>
+      <c r="G22" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>601</v>
+      </c>
+      <c r="C23" t="s">
+        <v>620</v>
+      </c>
+      <c r="G23" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>602</v>
+      </c>
+      <c r="C24" t="s">
+        <v>620</v>
+      </c>
+      <c r="G24" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>603</v>
+      </c>
+      <c r="C25" t="s">
+        <v>620</v>
+      </c>
+      <c r="G25" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>604</v>
+      </c>
+      <c r="C26" t="s">
+        <v>621</v>
+      </c>
+      <c r="G26" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>605</v>
+      </c>
+      <c r="C27" t="s">
+        <v>621</v>
+      </c>
+      <c r="G27" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>606</v>
+      </c>
+      <c r="C28" t="s">
+        <v>621</v>
+      </c>
+      <c r="G28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>607</v>
+      </c>
+      <c r="C29" t="s">
+        <v>621</v>
+      </c>
+      <c r="G29" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>608</v>
+      </c>
+      <c r="C30" t="s">
+        <v>621</v>
+      </c>
+      <c r="G30" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>609</v>
+      </c>
+      <c r="C31" t="s">
+        <v>621</v>
+      </c>
+      <c r="G31" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>610</v>
+      </c>
+      <c r="C32" t="s">
+        <v>621</v>
+      </c>
+      <c r="G32" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>611</v>
+      </c>
+      <c r="C33" t="s">
+        <v>621</v>
+      </c>
+      <c r="G33" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>612</v>
+      </c>
+      <c r="C34" t="s">
+        <v>622</v>
+      </c>
+      <c r="G34" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>613</v>
+      </c>
+      <c r="C35" t="s">
+        <v>622</v>
+      </c>
+      <c r="G35" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>614</v>
+      </c>
+      <c r="C36" t="s">
+        <v>622</v>
+      </c>
+      <c r="G36" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>615</v>
+      </c>
+      <c r="C37" t="s">
+        <v>622</v>
+      </c>
+      <c r="G37" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>616</v>
+      </c>
+      <c r="C38" t="s">
+        <v>622</v>
+      </c>
+      <c r="G38" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>617</v>
+      </c>
+      <c r="C39" t="s">
+        <v>622</v>
+      </c>
+      <c r="G39" t="s">
+        <v>649</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{15661FC6-38F3-4B96-AFA6-BAD4F1B284C8}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{5D9E3D52-9525-4CD6-86DE-9BF91FDD5790}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{186EB122-EDBA-44C0-99E6-F3E7D5CEB428}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{EACAD26D-7354-4D87-942E-2D7E2719B57F}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{9D7AAE0B-287D-4046-ACC8-4BBFBD71F3AF}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2638,31 +3312,31 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="C1" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D1" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E1" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F1" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="I1" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="J1" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2670,31 +3344,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="F2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="G2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="H2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="I2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="J2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2702,31 +3376,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C3" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E3" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="G3" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="H3" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="I3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="J3" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -2734,31 +3408,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="C4" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="D4" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="G4" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="H4" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="I4" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="J4" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2766,31 +3440,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="D5" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="F5" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="G5" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="H5" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="I5" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="J5" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +3485,7 @@
         <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2820,7 +3494,7 @@
         <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2828,19 +3502,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="D2" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F2" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2848,19 +3522,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2868,19 +3542,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -2888,19 +3562,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -2908,19 +3582,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="D6" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -2928,19 +3602,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="E7" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F7" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -2948,19 +3622,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F8" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -2968,19 +3642,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F9" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2988,19 +3662,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="D10" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="E10" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F10" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3008,19 +3682,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="C11" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="E11" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3563,10 +4237,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="D2" t="s">
         <v>126</v>
@@ -3575,10 +4249,10 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="G2" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="H2" t="s">
         <v>122</v>
@@ -3598,10 +4272,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="D3" t="s">
         <v>126</v>
@@ -3610,13 +4284,13 @@
         <v>127</v>
       </c>
       <c r="F3" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="G3" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="H3" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="I3" t="s">
         <v>128</v>
@@ -3633,10 +4307,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="C4" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="D4" t="s">
         <v>126</v>
@@ -3645,10 +4319,10 @@
         <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="H4" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="I4" t="s">
         <v>131</v>
@@ -3665,10 +4339,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
         <v>126</v>
@@ -3677,13 +4351,13 @@
         <v>133</v>
       </c>
       <c r="F5" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="G5" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="H5" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="I5" t="s">
         <v>134</v>
@@ -3700,10 +4374,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="D6" t="s">
         <v>136</v>
@@ -3712,10 +4386,10 @@
         <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="G6" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="H6" t="s">
         <v>138</v>
@@ -3735,10 +4409,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
         <v>136</v>
@@ -3747,10 +4421,10 @@
         <v>141</v>
       </c>
       <c r="F7" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="G7" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="I7" t="s">
         <v>142</v>
@@ -3767,10 +4441,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="C8" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="D8" t="s">
         <v>126</v>
@@ -3779,7 +4453,7 @@
         <v>144</v>
       </c>
       <c r="G8" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="H8" t="s">
         <v>138</v>
@@ -3799,10 +4473,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3811,10 +4485,10 @@
         <v>147</v>
       </c>
       <c r="F9" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="G9" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="I9" t="s">
         <v>148</v>
@@ -3867,7 +4541,7 @@
         <v>6625332615</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="D2" s="4">
         <v>3</v>
@@ -3876,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -3890,7 +4564,7 @@
         <v>6625331620</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="D3" s="6">
         <v>3</v>
@@ -3899,7 +4573,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G3" s="6">
         <v>1</v>
@@ -3913,7 +4587,7 @@
         <v>6625332616</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
@@ -3922,7 +4596,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G4" s="4">
         <v>2</v>
@@ -3936,7 +4610,7 @@
         <v>6625331635</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="D5" s="8">
         <v>3</v>
@@ -3945,7 +4619,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G5" s="8">
         <v>3</v>
@@ -3959,7 +4633,7 @@
         <v>6625331617</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="D6" s="10">
         <v>3</v>
@@ -3968,7 +4642,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G6" s="10">
         <v>3</v>
@@ -3982,7 +4656,7 @@
         <v>6625332650</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
@@ -3991,7 +4665,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -4005,7 +4679,7 @@
         <v>6625431653</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="D8" s="6">
         <v>3</v>
@@ -4014,7 +4688,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G8" s="6">
         <v>3</v>
@@ -4037,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G9" s="12">
         <v>4</v>
@@ -4051,7 +4725,7 @@
         <v>6625331618</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="D10" s="14">
         <v>3</v>
@@ -4060,7 +4734,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G10" s="14">
         <v>4</v>
@@ -4074,7 +4748,7 @@
         <v>6625232625</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="D11" s="8">
         <v>3</v>
@@ -4083,7 +4757,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G11" s="8">
         <v>4</v>
@@ -4097,7 +4771,7 @@
         <v>6625331634</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="D12" s="16">
         <v>3</v>
@@ -4106,7 +4780,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G12" s="16">
         <v>4</v>
@@ -4120,7 +4794,7 @@
         <v>6625131657</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="D13" s="10">
         <v>3</v>
@@ -4129,7 +4803,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G13" s="10">
         <v>4</v>
@@ -4143,7 +4817,7 @@
         <v>6625131660</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="D14" s="18">
         <v>3</v>
@@ -4152,7 +4826,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G14" s="18">
         <v>4</v>
@@ -4166,7 +4840,7 @@
         <v>6625331636</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
@@ -4175,7 +4849,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G15" s="4">
         <v>4</v>
@@ -4189,7 +4863,7 @@
         <v>6625332606</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="D16" s="12">
         <v>3</v>
@@ -4198,7 +4872,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G16" s="12">
         <v>5</v>
@@ -4212,7 +4886,7 @@
         <v>6625221622</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
@@ -4221,7 +4895,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="G17" s="14">
         <v>5</v>
@@ -4235,7 +4909,7 @@
         <v>6625322626</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="D18" s="8">
         <v>2</v>
@@ -4244,7 +4918,7 @@
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G18" s="8">
         <v>5</v>
@@ -4258,7 +4932,7 @@
         <v>6625324628</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="D19" s="16">
         <v>2</v>
@@ -4267,7 +4941,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G19" s="16">
         <v>5</v>
@@ -4281,7 +4955,7 @@
         <v>6625332630</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>551</v>
+        <v>531</v>
       </c>
       <c r="D20" s="10">
         <v>3</v>
@@ -4290,7 +4964,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G20" s="10">
         <v>5</v>
@@ -4304,7 +4978,7 @@
         <v>6625331649</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="D21" s="18">
         <v>3</v>
@@ -4313,7 +4987,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G21" s="18">
         <v>5</v>
@@ -4327,7 +5001,7 @@
         <v>6625331656</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -4336,7 +5010,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G22" s="4">
         <v>5</v>
@@ -4350,7 +5024,7 @@
         <v>6625221605</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
@@ -4359,7 +5033,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="G23" s="6">
         <v>6</v>
@@ -4373,7 +5047,7 @@
         <v>6625332612</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="D24" s="12">
         <v>3</v>
@@ -4382,7 +5056,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G24" s="12">
         <v>6</v>
@@ -4396,7 +5070,7 @@
         <v>6625321614</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -4405,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
@@ -4419,7 +5093,7 @@
         <v>6625332623</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="D26" s="8">
         <v>3</v>
@@ -4428,7 +5102,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G26" s="8">
         <v>6</v>
@@ -4442,7 +5116,7 @@
         <v>6625241624</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="D27" s="16">
         <v>4</v>
@@ -4451,7 +5125,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G27" s="16">
         <v>6</v>
@@ -4465,7 +5139,7 @@
         <v>6625321633</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="D28" s="10">
         <v>2</v>
@@ -4474,7 +5148,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G28" s="10">
         <v>6</v>
@@ -4488,7 +5162,7 @@
         <v>6625321647</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="D29" s="18">
         <v>2</v>
@@ -4497,7 +5171,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="G29" s="18">
         <v>6</v>
@@ -4511,7 +5185,7 @@
         <v>6625332651</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="D30" s="4">
         <v>3</v>
@@ -4520,7 +5194,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G30" s="4">
         <v>6</v>
@@ -4534,7 +5208,7 @@
         <v>6625322603</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D31" s="6">
         <v>3</v>
@@ -4543,7 +5217,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G31" s="6">
         <v>7</v>
@@ -4566,7 +5240,7 @@
         <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G32" s="12">
         <v>7</v>
@@ -4580,7 +5254,7 @@
         <v>6625422627</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -4589,7 +5263,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G33" s="14">
         <v>7</v>
@@ -4603,7 +5277,7 @@
         <v>6625421631</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="D34" s="8">
         <v>2</v>
@@ -4612,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G34" s="8">
         <v>7</v>
@@ -4626,7 +5300,7 @@
         <v>6625421632</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D35" s="16">
         <v>2</v>
@@ -4635,7 +5309,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G35" s="16">
         <v>7</v>
@@ -4649,7 +5323,7 @@
         <v>6625322648</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="D36" s="10">
         <v>2</v>
@@ -4658,7 +5332,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G36" s="10">
         <v>7</v>
@@ -4672,7 +5346,7 @@
         <v>6625745652</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="D37" s="18">
         <v>4</v>
@@ -4681,7 +5355,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G37" s="18">
         <v>7</v>
@@ -4695,7 +5369,7 @@
         <v>6625321638</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
@@ -4704,7 +5378,7 @@
         <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="G38" s="4">
         <v>7</v>
@@ -4718,7 +5392,7 @@
         <v>6625244629</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="D39" s="12">
         <v>4</v>
@@ -4727,7 +5401,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="G39" s="12">
         <v>8</v>
@@ -4750,7 +5424,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="G40" s="14">
         <v>8</v>
@@ -4792,16 +5466,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="C2" t="s">
         <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E2" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4809,13 +5483,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="C3" t="s">
         <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="E3" t="s">
         <v>160</v>
@@ -4826,13 +5500,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="C4" t="s">
         <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E4" t="s">
         <v>160</v>
@@ -4843,13 +5517,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="C5" t="s">
         <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="E5" t="s">
         <v>160</v>
@@ -4860,13 +5534,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="E6" t="s">
         <v>162</v>
@@ -4877,13 +5551,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="C7" t="s">
         <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E7" t="s">
         <v>160</v>
@@ -4894,16 +5568,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="C8" t="s">
         <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="E8" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4911,13 +5585,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="E9" t="s">
         <v>162</v>
@@ -4928,13 +5602,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="E10" t="s">
         <v>162</v>
@@ -4945,13 +5619,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="C11" t="s">
         <v>164</v>
       </c>
       <c r="D11" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E11" t="s">
         <v>162</v>
@@ -4962,13 +5636,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="C12" t="s">
         <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="E12" t="s">
         <v>160</v>
@@ -4979,13 +5653,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="C13" t="s">
         <v>165</v>
       </c>
       <c r="D13" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="E13" t="s">
         <v>160</v>
@@ -4996,16 +5670,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="C14" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="D14" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="E14" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -5013,13 +5687,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="C15" t="s">
         <v>161</v>
       </c>
       <c r="D15" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -5030,13 +5704,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>582</v>
+        <v>562</v>
       </c>
       <c r="C16" t="s">
         <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="E16" t="s">
         <v>162</v>
@@ -5047,16 +5721,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="C17" t="s">
         <v>161</v>
       </c>
       <c r="D17" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E17" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -5064,16 +5738,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="C18" t="s">
         <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E18" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -5081,13 +5755,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="E19" t="s">
         <v>162</v>
@@ -5098,13 +5772,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="E20" t="s">
         <v>162</v>
@@ -5115,16 +5789,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="C21" t="s">
         <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="E21" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -5132,16 +5806,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="C22" t="s">
         <v>161</v>
       </c>
       <c r="D22" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="E22" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -5149,16 +5823,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="C23" t="s">
         <v>161</v>
       </c>
       <c r="D23" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="E23" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -5212,22 +5886,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C2" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="G2" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -5235,22 +5909,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="D3" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="G3" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -5258,19 +5932,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="D4" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -5278,19 +5952,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D5" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5298,22 +5972,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="G6" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -5321,22 +5995,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="G7" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -5344,22 +6018,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="D8" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="G8" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -5367,22 +6041,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="C9" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="G9" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -5390,22 +6064,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="D10" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="G10" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -5413,22 +6087,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="G11" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -5436,22 +6110,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="C12" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="D12" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G12" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -5459,22 +6133,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="C13" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G13" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -5482,22 +6156,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="C14" t="s">
+        <v>403</v>
+      </c>
+      <c r="D14" t="s">
         <v>423</v>
-      </c>
-      <c r="D14" t="s">
-        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G14" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -5505,22 +6179,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D15" t="s">
         <v>424</v>
-      </c>
-      <c r="D15" t="s">
-        <v>444</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G15" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5528,22 +6202,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D16" t="s">
         <v>425</v>
-      </c>
-      <c r="D16" t="s">
-        <v>445</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G16" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -5551,22 +6225,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="D17" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G17" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -5574,22 +6248,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="D18" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G18" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -5597,22 +6271,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="C19" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="D19" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G19" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -5620,22 +6294,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="D20" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G20" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -5643,22 +6317,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="D21" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G21" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -5666,22 +6340,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="C22" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" t="s">
         <v>423</v>
-      </c>
-      <c r="D22" t="s">
-        <v>443</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
       </c>
       <c r="F22" t="s">
+        <v>436</v>
+      </c>
+      <c r="G22" t="s">
         <v>456</v>
-      </c>
-      <c r="G22" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -5689,19 +6363,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="C23" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="D23" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -5709,19 +6383,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C24" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="D24" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -5729,10 +6403,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="C25" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="D25">
         <v>2024</v>
@@ -5741,7 +6415,7 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -5749,10 +6423,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D26">
         <v>2025</v>
@@ -5761,7 +6435,7 @@
         <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -5769,10 +6443,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C27" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="D27">
         <v>2025</v>
@@ -5781,10 +6455,10 @@
         <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="G27" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -5792,10 +6466,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="C28" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="D28">
         <v>2024</v>
@@ -5804,10 +6478,10 @@
         <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="G28" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -5815,10 +6489,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="C29" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D29">
         <v>2023</v>
@@ -5827,10 +6501,10 @@
         <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="G29" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -5838,10 +6512,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="C30" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="D30">
         <v>2026</v>
@@ -5850,10 +6524,10 @@
         <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="G30" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -5861,10 +6535,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="C31" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="D31">
         <v>2026</v>
@@ -5873,10 +6547,10 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="G31" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -5884,10 +6558,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="C32" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="D32">
         <v>2025</v>
@@ -5896,10 +6570,10 @@
         <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="G32" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -5907,10 +6581,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C33" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="D33">
         <v>2024</v>
@@ -5919,10 +6593,10 @@
         <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="G33" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -5930,10 +6604,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="C34" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="D34">
         <v>2024</v>
@@ -5942,10 +6616,10 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="G34" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="145" x14ac:dyDescent="0.35">
@@ -5953,10 +6627,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="C35" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="D35">
         <v>2024</v>
@@ -5965,10 +6639,10 @@
         <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -5976,10 +6650,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C36" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D36">
         <v>2023</v>
@@ -5988,10 +6662,10 @@
         <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="G36" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -6271,22 +6945,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="C2" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="G2" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="H2" t="s">
         <v>195</v>
@@ -6303,22 +6977,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C3" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="D3" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="G3" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="H3" t="s">
         <v>198</v>
@@ -6329,22 +7003,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="C4" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D4" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="G4" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="H4" t="s">
         <v>199</v>
@@ -6358,22 +7032,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="C5" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E5" t="s">
         <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="G5" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -6381,22 +7055,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="D6" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="G6" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -6404,22 +7078,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="C7" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D7" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="G7" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -6427,22 +7101,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="C8" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="D8" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="G8" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -6450,22 +7124,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="C9" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D9" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="G9" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -6473,22 +7147,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="C10" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="G10" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -6496,22 +7170,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="C11" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="G11" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -6519,22 +7193,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="G12" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -6542,19 +7216,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="C13" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -6562,19 +7236,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="C14" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="D14" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -6582,19 +7256,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="D15" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -6602,19 +7276,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="C16" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D16" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -6622,19 +7296,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="C17" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D17" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -6642,19 +7316,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="C18" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="D18" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -6662,19 +7336,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="C19" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D19" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
